--- a/JREポイント完全データベース_統合版_v5.xlsx
+++ b/JREポイント完全データベース_統合版_v5.xlsx
@@ -3372,7 +3372,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>衣料/子供服</t>
+          <t>衣料</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>生活雑貨/衣料/子供服/食品</t>
+          <t>生活雑貨/家具/衣料</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>衣料/子供服</t>
+          <t>衣料</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>生活雑貨/衣料/子供服/食品</t>
+          <t>生活雑貨/家具/衣料</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E941"/>
+  <dimension ref="A1:E937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32102,20 +32102,24 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>ユニクロ エキュート品川</t>
+          <t>TAKUJI STATION</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -32125,7 +32129,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>TAKUJI STATION</t>
+          <t>めばえ教室</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -32140,7 +32144,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>7F</t>
         </is>
       </c>
     </row>
@@ -32152,7 +32156,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>無印良品</t>
+          <t>ミキハウスキッズパル</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -32167,19 +32171,19 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>4F</t>
+          <t>7F</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>家具</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>ユニクロ</t>
+          <t>無印良品</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -32194,73 +32198,65 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>4F</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>家具</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>めばえ教室</t>
+          <t>JOURNAL STANDARD FURNITURE</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr">
-        <is>
-          <t>7F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>家具</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>ミキハウスキッズパル</t>
+          <t>無印良品</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr">
-        <is>
-          <t>7F</t>
-        </is>
-      </c>
+          <t>ニュウマン横浜</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>家具</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>無印良品</t>
+          <t>unico</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -32278,22 +32274,22 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>家具</t>
+          <t>弁当</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>JOURNAL STANDARD FURNITURE</t>
+          <t>つばめグリルDELI</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E492" t="inlineStr"/>
@@ -32301,22 +32297,22 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>家具</t>
+          <t>弁当</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>unico</t>
+          <t>ヴィ パレット</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E493" t="inlineStr"/>
@@ -32329,7 +32325,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>つばめグリルDELI</t>
+          <t>いなりすし専門店 豆狸</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -32352,7 +32348,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>ヴィ パレット</t>
+          <t>とんかつ まい泉</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -32375,7 +32371,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>いなりすし専門店 豆狸</t>
+          <t>てとて</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -32398,7 +32394,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>とんかつ まい泉</t>
+          <t>千駄木腰塚</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -32421,7 +32417,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>てとて</t>
+          <t>軽井沢いぶる</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -32444,7 +32440,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>千駄木腰塚</t>
+          <t>バル マルシェ コダマ</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -32467,7 +32463,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>軽井沢いぶる</t>
+          <t>パオパオ</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -32490,7 +32486,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>バル マルシェ コダマ</t>
+          <t>なだ万 厨房</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -32513,7 +32509,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>パオパオ</t>
+          <t>ゑびすDaikoku</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -32536,7 +32532,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>なだ万 厨房</t>
+          <t>日本橋だし場 OBENTO</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -32559,7 +32555,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>ゑびすDaikoku</t>
+          <t>日本橋 天丼 天むす 金子半之助</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -32582,7 +32578,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>日本橋だし場 OBENTO</t>
+          <t>肉卸 小島</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -32605,7 +32601,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>日本橋 天丼 天むす 金子半之助</t>
+          <t>刷毛じょうゆ 海苔弁山登り</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -32628,7 +32624,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>肉卸 小島</t>
+          <t>東急ストア フードステーションミニ</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -32651,7 +32647,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>刷毛じょうゆ 海苔弁山登り</t>
+          <t>魚力 海鮮寿司</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -32674,7 +32670,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>東急ストア フードステーションミニ</t>
+          <t>アール・エフ・ワン</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -32697,7 +32693,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>魚力 海鮮寿司</t>
+          <t>神戸コロッケ</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -32720,7 +32716,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>アール・エフ・ワン</t>
+          <t>イーション</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -32743,7 +32739,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>神戸コロッケ</t>
+          <t>サンドイッチハウス メルヘン</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -32766,7 +32762,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>イーション</t>
+          <t>鳥麻</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -32789,7 +32785,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>サンドイッチハウス メルヘン</t>
+          <t>塚田農場OBENTO&amp;DELI</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -32812,7 +32808,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>鳥麻</t>
+          <t>おむすび百千</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -32835,7 +32831,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>塚田農場OBENTO&amp;DELI</t>
+          <t>カンナムキンパ</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -32858,7 +32854,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>おむすび百千</t>
+          <t>ほんのり屋</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -32881,7 +32877,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>カンナムキンパ</t>
+          <t>地雷也</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -32904,7 +32900,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>ほんのり屋</t>
+          <t>シターラ</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -32927,20 +32923,24 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>地雷也</t>
+          <t>昇龍園</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E520" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -32950,20 +32950,24 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>シターラ</t>
+          <t>とんかつ和幸</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E521" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -32973,7 +32977,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>昇龍園</t>
+          <t>跳ね鯛</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -33000,7 +33004,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>とんかつ和幸</t>
+          <t>チキン・ディッシュ</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -33027,7 +33031,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>跳ね鯛</t>
+          <t>好餃子 ハオチャオズ</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -33054,7 +33058,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>チキン・ディッシュ</t>
+          <t>日本一</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -33081,7 +33085,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>好餃子 ハオチャオズ</t>
+          <t>グリーン・グルメ</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -33108,7 +33112,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>日本一</t>
+          <t>崎陽軒</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -33135,7 +33139,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>グリーン・グルメ</t>
+          <t>のり弁・UOHIDE</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -33162,7 +33166,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>崎陽軒</t>
+          <t>K-SOZAI</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -33189,7 +33193,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>のり弁・UOHIDE</t>
+          <t>アール・エフ・ワン</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -33204,7 +33208,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -33216,7 +33220,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>K-SOZAI</t>
+          <t>パオパオ</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -33231,7 +33235,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -33243,7 +33247,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>アール・エフ・ワン</t>
+          <t>イーション</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -33270,7 +33274,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>パオパオ</t>
+          <t>横浜 昇龍園</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -33297,7 +33301,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>イーション</t>
+          <t>日本一</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -33324,7 +33328,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>横浜 昇龍園</t>
+          <t>とんかつ まい泉</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -33351,7 +33355,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>日本一</t>
+          <t>豆狸</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -33378,7 +33382,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>とんかつ まい泉</t>
+          <t>ほんのり屋</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -33405,7 +33409,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>豆狸</t>
+          <t>焼魚舗 神戸 あかり</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -33432,7 +33436,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>ほんのり屋</t>
+          <t>明洞デリ</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -33459,7 +33463,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>焼魚舗 神戸 あかり</t>
+          <t>おむすび権米衛</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -33474,7 +33478,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -33486,24 +33490,20 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>明洞デリ</t>
+          <t>重慶飯店 GIFT &amp; DELI</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>北側改札内3F</t>
-        </is>
-      </c>
+          <t>CIAL横浜</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -33513,24 +33513,20 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>おむすび権米衛</t>
+          <t>グリーン・グルメ</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
+          <t>CIAL横浜</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -33540,7 +33536,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>重慶飯店 GIFT &amp; DELI</t>
+          <t>博多 肉の壱丁田</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -33563,7 +33559,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>グリーン・グルメ</t>
+          <t>はまけい</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -33586,7 +33582,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>博多 肉の壱丁田</t>
+          <t>勝烈庵</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -33609,7 +33605,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>はまけい</t>
+          <t>三ツ星弁当 頂</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -33632,7 +33628,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>勝烈庵</t>
+          <t>つばめグリルDELI</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -33655,7 +33651,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>三ツ星弁当 頂</t>
+          <t>塚田農場OBENTO＆DELI</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -33678,7 +33674,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>つばめグリルDELI</t>
+          <t>五十嵐</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -33701,7 +33697,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>塚田農場OBENTO＆DELI</t>
+          <t>チャオタイの屋台弁当</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -33724,7 +33720,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>五十嵐</t>
+          <t>カンナムデリ</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -33747,7 +33743,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>チャオタイの屋台弁当</t>
+          <t>イーション</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -33765,22 +33761,22 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>弁当</t>
+          <t>惣菜</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>カンナムデリ</t>
+          <t>つばめグリルDELI</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E553" t="inlineStr"/>
@@ -33788,22 +33784,22 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>弁当</t>
+          <t>惣菜</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>イーション</t>
+          <t>ヴィ パレット</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E554" t="inlineStr"/>
@@ -33816,7 +33812,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>つばめグリルDELI</t>
+          <t>いなりすし専門店 豆狸</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -33839,7 +33835,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>ヴィ パレット</t>
+          <t>とんかつ まい泉</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -33862,7 +33858,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>いなりすし専門店 豆狸</t>
+          <t>てとて</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -33885,7 +33881,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>とんかつ まい泉</t>
+          <t>千駄木腰塚</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -33908,7 +33904,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>てとて</t>
+          <t>軽井沢いぶる</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -33931,7 +33927,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>千駄木腰塚</t>
+          <t>バル マルシェ コダマ</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -33954,7 +33950,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>軽井沢いぶる</t>
+          <t>パオパオ</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -33977,7 +33973,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>バル マルシェ コダマ</t>
+          <t>なだ万 厨房</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -34000,7 +33996,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>パオパオ</t>
+          <t>ゑびすDaikoku</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -34023,7 +34019,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>なだ万 厨房</t>
+          <t>日本橋だし場 OBENTO</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -34046,7 +34042,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>ゑびすDaikoku</t>
+          <t>日本橋 天丼 天むす 金子半之助</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -34069,7 +34065,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>日本橋だし場 OBENTO</t>
+          <t>肉卸 小島</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -34092,7 +34088,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>日本橋 天丼 天むす 金子半之助</t>
+          <t>刷毛じょうゆ 海苔弁山登り</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -34115,7 +34111,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>肉卸 小島</t>
+          <t>東急ストア フードステーションミニ</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -34138,7 +34134,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>刷毛じょうゆ 海苔弁山登り</t>
+          <t>魚力 海鮮寿司</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -34161,7 +34157,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>東急ストア フードステーションミニ</t>
+          <t>アール・エフ・ワン</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -34184,7 +34180,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>魚力 海鮮寿司</t>
+          <t>神戸コロッケ</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -34207,7 +34203,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>アール・エフ・ワン</t>
+          <t>イーション</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -34230,7 +34226,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>神戸コロッケ</t>
+          <t>サンドイッチハウス メルヘン</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -34253,7 +34249,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>イーション</t>
+          <t>鳥麻</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -34276,7 +34272,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>サンドイッチハウス メルヘン</t>
+          <t>塚田農場OBENTO&amp;DELI</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -34299,7 +34295,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>鳥麻</t>
+          <t>おむすび百千</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -34322,7 +34318,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>塚田農場OBENTO&amp;DELI</t>
+          <t>カンナムキンパ</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -34345,7 +34341,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>おむすび百千</t>
+          <t>ほんのり屋</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -34368,7 +34364,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>カンナムキンパ</t>
+          <t>地雷也</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -34391,7 +34387,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>ほんのり屋</t>
+          <t>シターラ</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -34414,20 +34410,24 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>地雷也</t>
+          <t>昇龍園</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E581" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -34437,20 +34437,24 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>シターラ</t>
+          <t>とんかつ和幸</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E582" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -34460,7 +34464,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>昇龍園</t>
+          <t>跳ね鯛</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -34487,7 +34491,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>とんかつ和幸</t>
+          <t>チキン・ディッシュ</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -34514,7 +34518,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>跳ね鯛</t>
+          <t>好餃子 ハオチャオズ</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -34541,7 +34545,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>チキン・ディッシュ</t>
+          <t>日本一</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -34568,7 +34572,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>好餃子 ハオチャオズ</t>
+          <t>グリーン・グルメ</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -34595,7 +34599,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>日本一</t>
+          <t>崎陽軒</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -34622,7 +34626,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>グリーン・グルメ</t>
+          <t>のり弁・UOHIDE</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -34649,7 +34653,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>崎陽軒</t>
+          <t>K-SOZAI</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -34676,7 +34680,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>のり弁・UOHIDE</t>
+          <t>アール・エフ・ワン</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -34691,7 +34695,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34707,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>K-SOZAI</t>
+          <t>パオパオ</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -34718,7 +34722,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -34730,7 +34734,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>アール・エフ・ワン</t>
+          <t>イーション</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -34757,7 +34761,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>パオパオ</t>
+          <t>横浜 昇龍園</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -34784,7 +34788,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>イーション</t>
+          <t>日本一</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -34811,7 +34815,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>横浜 昇龍園</t>
+          <t>とんかつ まい泉</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -34838,7 +34842,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>日本一</t>
+          <t>豆狸</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -34865,7 +34869,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>とんかつ まい泉</t>
+          <t>ほんのり屋</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -34892,7 +34896,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>豆狸</t>
+          <t>焼魚舗 神戸 あかり</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -34919,7 +34923,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>ほんのり屋</t>
+          <t>明洞デリ</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -34946,7 +34950,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>焼魚舗 神戸 あかり</t>
+          <t>おむすび権米衛</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -34961,7 +34965,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -34973,24 +34977,20 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>明洞デリ</t>
+          <t>重慶飯店 GIFT &amp; DELI</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E602" t="inlineStr">
-        <is>
-          <t>北側改札内3F</t>
-        </is>
-      </c>
+          <t>CIAL横浜</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -35000,24 +35000,20 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>おむすび権米衛</t>
+          <t>グリーン・グルメ</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
+          <t>CIAL横浜</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -35027,7 +35023,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>重慶飯店 GIFT &amp; DELI</t>
+          <t>博多 肉の壱丁田</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -35050,7 +35046,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>グリーン・グルメ</t>
+          <t>はまけい</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -35073,7 +35069,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>博多 肉の壱丁田</t>
+          <t>勝烈庵</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -35096,7 +35092,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>はまけい</t>
+          <t>三ツ星弁当 頂</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -35119,7 +35115,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>勝烈庵</t>
+          <t>つばめグリルDELI</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -35142,7 +35138,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>三ツ星弁当 頂</t>
+          <t>塚田農場OBENTO＆DELI</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -35165,7 +35161,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>つばめグリルDELI</t>
+          <t>五十嵐</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -35188,7 +35184,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>塚田農場OBENTO＆DELI</t>
+          <t>チャオタイの屋台弁当</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -35211,7 +35207,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>五十嵐</t>
+          <t>カンナムデリ</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -35234,7 +35230,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>チャオタイの屋台弁当</t>
+          <t>イーション</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -35252,22 +35248,22 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>惣菜</t>
+          <t>文具</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>カンナムデリ</t>
+          <t>エディト・トロワ・シス・サンク</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E614" t="inlineStr"/>
@@ -35275,12 +35271,12 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>惣菜</t>
+          <t>文具</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>イーション</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -35290,7 +35286,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E615" t="inlineStr"/>
@@ -35303,17 +35299,17 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>エディト・トロワ・シス・サンク</t>
+          <t>世界堂</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E616" t="inlineStr"/>
@@ -35321,22 +35317,22 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>文具</t>
+          <t>書籍</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>ブックコンパス</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E617" t="inlineStr"/>
@@ -35344,25 +35340,29 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>文具</t>
+          <t>書籍</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>世界堂</t>
+          <t>有隣堂</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E618" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>4F</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -35372,17 +35372,17 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>ブックコンパス</t>
+          <t>有隣堂</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E619" t="inlineStr"/>
@@ -35390,49 +35390,45 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>書籍</t>
+          <t>生活雑貨</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>有隣堂</t>
+          <t>ヴィド-ポッシュ ドゥ セピカ</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E620" t="inlineStr">
-        <is>
-          <t>4F</t>
-        </is>
-      </c>
+          <t>アトレ品川</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>書籍</t>
+          <t>生活雑貨</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>有隣堂</t>
+          <t>イア パピヨネ</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E621" t="inlineStr"/>
@@ -35445,7 +35441,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>ヴィド-ポッシュ ドゥ セピカ</t>
+          <t>エディト・トロワ・シス・サンク</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -35468,7 +35464,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>イア パピヨネ</t>
+          <t>RANDA</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -35491,7 +35487,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>エディト・トロワ・シス・サンク</t>
+          <t>中川政七商店</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -35514,7 +35510,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>RANDA</t>
+          <t>スミス</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -35524,7 +35520,7 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
@@ -35537,7 +35533,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>中川政七商店</t>
+          <t>フルーツギャザリング</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -35547,7 +35543,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
@@ -35560,7 +35556,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>スミス</t>
+          <t>ポータースタンド</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -35583,7 +35579,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>フルーツギャザリング</t>
+          <t>La Maison Concierge</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -35606,7 +35602,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>ポータースタンド</t>
+          <t>Tiny CRAFTS</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -35629,20 +35625,24 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>La Maison Concierge</t>
+          <t>カメラのキタムラ</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E630" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -35652,20 +35652,24 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Tiny CRAFTS</t>
+          <t>エンハーブ</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E631" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -35675,7 +35679,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>カメラのキタムラ</t>
+          <t>プラザ</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -35690,7 +35694,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -35702,7 +35706,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>エンハーブ</t>
+          <t>3COINS＋plus</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -35729,7 +35733,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>プラザ</t>
+          <t>DaisyLewis</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -35756,7 +35760,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>3COINS＋plus</t>
+          <t>ピロースタンド</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -35771,7 +35775,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -35783,7 +35787,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>DaisyLewis</t>
+          <t>スミス</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -35798,7 +35802,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -35810,7 +35814,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>ピロースタンド</t>
+          <t>アフタヌーンティー・ギフト&amp;リビング</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -35825,7 +35829,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -35837,7 +35841,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>スミス</t>
+          <t>バースデイ・バー</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -35864,7 +35868,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>アフタヌーンティー・ギフト&amp;リビング</t>
+          <t>ハンズ</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -35879,7 +35883,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>4F</t>
         </is>
       </c>
     </row>
@@ -35891,7 +35895,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>バースデイ・バー</t>
+          <t>フライング タイガー コペンハーゲン</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -35906,7 +35910,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>4F</t>
         </is>
       </c>
     </row>
@@ -35918,7 +35922,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>ハンズ</t>
+          <t>無印良品</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -35945,7 +35949,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>フライング タイガー コペンハーゲン</t>
+          <t>有隣堂</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -35972,24 +35976,20 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>無印良品</t>
+          <t>有隣堂</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E643" t="inlineStr">
-        <is>
-          <t>4F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -35999,24 +35999,20 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>有隣堂</t>
+          <t>PLAZA</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E644" t="inlineStr">
-        <is>
-          <t>4F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -36026,7 +36022,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>有隣堂</t>
+          <t>ATELIER</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -36049,7 +36045,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>PLAZA</t>
+          <t>enherb</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -36072,7 +36068,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>ATELIER</t>
+          <t>中川政七商店</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -36095,7 +36091,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>enherb</t>
+          <t>BIRTHDAY BAR</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -36118,7 +36114,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>中川政七商店</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -36141,7 +36137,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>BIRTHDAY BAR</t>
+          <t>世界堂</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -36164,7 +36160,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>無印良品</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -36174,7 +36170,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E651" t="inlineStr"/>
@@ -36187,7 +36183,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>世界堂</t>
+          <t>TENERITA</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -36197,7 +36193,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E652" t="inlineStr"/>
@@ -36210,7 +36206,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>無印良品</t>
+          <t>薫玉堂</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -36228,22 +36224,22 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>生活雑貨</t>
+          <t>花</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>TENERITA</t>
+          <t>Hibiya-Kadan Style プラスエフ</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E654" t="inlineStr"/>
@@ -36251,22 +36247,22 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>生活雑貨</t>
+          <t>花</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>薫玉堂</t>
+          <t>青山フラワーマーケット</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
@@ -36279,20 +36275,24 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Hibiya-Kadan Style プラスエフ</t>
+          <t>モンソー フルール</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
-        </is>
-      </c>
-      <c r="E656" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -36307,15 +36307,19 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E657" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -36325,7 +36329,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>モンソー フルール</t>
+          <t>青山フラワーマーケット ミドリギゲート店</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -36340,7 +36344,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -36352,24 +36356,20 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>青山フラワーマーケット</t>
+          <t>フルラージュアン</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E659" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -36379,44 +36379,40 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>青山フラワーマーケット ミドリギゲート店</t>
+          <t>FLEURISTE BON MARCHE</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E660" t="inlineStr">
-        <is>
-          <t>3F</t>
-        </is>
-      </c>
+          <t>CIAL横浜</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>花</t>
+          <t>衣料</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>フルラージュアン</t>
+          <t>タビオ</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E661" t="inlineStr"/>
@@ -36424,22 +36420,22 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>花</t>
+          <t>衣料</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>FLEURISTE BON MARCHE</t>
+          <t>メーカーズシャツ鎌倉</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E662" t="inlineStr"/>
@@ -36452,7 +36448,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>タビオ</t>
+          <t>ハミングバード</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -36462,7 +36458,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E663" t="inlineStr"/>
@@ -36475,7 +36471,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>メーカーズシャツ鎌倉</t>
+          <t>ユニクロ エキュート品川</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -36485,7 +36481,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E664" t="inlineStr"/>
@@ -36498,20 +36494,24 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>ハミングバード</t>
+          <t>ユナイテッドアローズ グリーンレーベルリラクシング ウィメン</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E665" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -36521,20 +36521,24 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>ユニクロ エキュート品川</t>
+          <t>パサージュ ミニョン</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E666" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -36544,7 +36548,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>ユナイテッドアローズ グリーンレーベルリラクシング ウィメン</t>
+          <t>マリークワント</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -36571,7 +36575,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>パサージュ ミニョン</t>
+          <t>ブルーブルーエ</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -36598,7 +36602,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>マリークワント</t>
+          <t>サマンサモスモス</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -36613,7 +36617,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -36625,7 +36629,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>ブルーブルーエ</t>
+          <t>ローリーズファーム</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -36640,7 +36644,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -36652,7 +36656,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>サマンサモスモス</t>
+          <t>アルシーヴ</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -36679,7 +36683,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>ローリーズファーム</t>
+          <t>ヘザー</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -36706,7 +36710,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>アルシーヴ</t>
+          <t>ページボーイ</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -36733,7 +36737,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>ヘザー</t>
+          <t>ジーナシス</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -36760,7 +36764,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>ページボーイ</t>
+          <t>クリア</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -36787,7 +36791,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>ジーナシス</t>
+          <t>グラシア ルッソ</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -36814,7 +36818,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>クリア</t>
+          <t>グレープフルーツ ムーン</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -36841,7 +36845,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>グラシア ルッソ</t>
+          <t>チュチュアンナ グランデ</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -36868,7 +36872,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>グレープフルーツ ムーン</t>
+          <t>ルトリオ アバハウス</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -36883,7 +36887,7 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -36895,7 +36899,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>チュチュアンナ グランデ</t>
+          <t>ストラ</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -36910,7 +36914,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -36922,7 +36926,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>ルトリオ アバハウス</t>
+          <t>プロポーション</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -36949,7 +36953,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>ストラ</t>
+          <t>ストロベリーフィールズ</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -36976,7 +36980,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>プロポーション</t>
+          <t>ルーニィ</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -37003,7 +37007,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>ストロベリーフィールズ</t>
+          <t>ハレ</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -37030,7 +37034,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>ルーニィ</t>
+          <t>ドゥアルシーヴ</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -37057,7 +37061,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>ハレ</t>
+          <t>テチチ</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -37084,7 +37088,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>ドゥアルシーヴ</t>
+          <t>サックスバー</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -37111,7 +37115,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>テチチ</t>
+          <t>バンヤードストーム</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -37138,7 +37142,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>サックスバー</t>
+          <t>GALLEST</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -37165,7 +37169,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>バンヤードストーム</t>
+          <t>スリーフォータイム</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -37192,7 +37196,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>GALLEST</t>
+          <t>アンフィ</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -37219,7 +37223,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>スリーフォータイム</t>
+          <t>リサマリ</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -37246,7 +37250,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>アンフィ</t>
+          <t>シップス</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -37273,7 +37277,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>リサマリ</t>
+          <t>アーバンリサーチ ドアーズ</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -37300,7 +37304,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>シップス</t>
+          <t>無印良品</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -37315,7 +37319,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>4F</t>
         </is>
       </c>
     </row>
@@ -37327,7 +37331,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>アーバンリサーチ ドアーズ</t>
+          <t>アンテ バイ アンテシュクレ</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -37342,7 +37346,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>4F</t>
         </is>
       </c>
     </row>
@@ -37354,7 +37358,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>無印良品</t>
+          <t>レイジブルー</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -37381,7 +37385,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>アンテ バイ アンテシュクレ</t>
+          <t>ロペピクニック</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -37408,7 +37412,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>レイジブルー</t>
+          <t>エルーラ</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -37435,7 +37439,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>ロペピクニック</t>
+          <t>ミッシュマッシュ</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -37462,7 +37466,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>エルーラ</t>
+          <t>ユニクロ</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -37477,7 +37481,7 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>4F</t>
+          <t>5F</t>
         </is>
       </c>
     </row>
@@ -37489,7 +37493,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>ミッシュマッシュ</t>
+          <t>エメ</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -37504,7 +37508,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>4F</t>
+          <t>6F</t>
         </is>
       </c>
     </row>
@@ -37516,7 +37520,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>ユニクロ</t>
+          <t>ハニーズ</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -37531,7 +37535,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>6F</t>
         </is>
       </c>
     </row>
@@ -37543,7 +37547,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>エメ</t>
+          <t>オリヒカ</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -37570,24 +37574,20 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>ハニーズ</t>
+          <t>Deuxième Classe</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E705" t="inlineStr">
-        <is>
-          <t>6F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -37597,24 +37597,20 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>オリヒカ</t>
+          <t>martinique</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E706" t="inlineStr">
-        <is>
-          <t>6F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -37624,7 +37620,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Deuxième Classe</t>
+          <t>MilaOwen</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -37647,7 +37643,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>martinique</t>
+          <t>EIMY ISTOIRE</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -37670,7 +37666,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>MilaOwen</t>
+          <t>BABYLONE</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -37693,7 +37689,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>EIMY ISTOIRE</t>
+          <t>ánuans</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -37716,7 +37712,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>BABYLONE</t>
+          <t>グレースコンチネンタル</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -37739,7 +37735,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>ánuans</t>
+          <t>LILY BROWN</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -37762,7 +37758,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>グレースコンチネンタル</t>
+          <t>FURFUR</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -37785,7 +37781,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>LILY BROWN</t>
+          <t>SHENERY</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -37808,7 +37804,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>FURFUR</t>
+          <t>FRAMeWORK</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -37831,7 +37827,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>SHENERY</t>
+          <t>LOUNGEDRESS</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -37854,7 +37850,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>FRAMeWORK</t>
+          <t>LAGUNAMOON</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -37877,7 +37873,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>LOUNGEDRESS</t>
+          <t>FRAY I.D</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -37900,7 +37896,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>LAGUNAMOON</t>
+          <t>GALLARDAGALANTE</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -37923,7 +37919,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>FRAY I.D</t>
+          <t>allureville</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -37946,7 +37942,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>GALLARDAGALANTE</t>
+          <t>Arpege story</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -37969,7 +37965,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>allureville</t>
+          <t>Apuweiser-riche</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -37992,7 +37988,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Arpege story</t>
+          <t>SNIDEL</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -38015,7 +38011,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Apuweiser-riche</t>
+          <t>ETRÉ TOKYO</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -38038,7 +38034,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>SNIDEL</t>
+          <t>gelato pique</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -38061,7 +38057,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>ETRÉ TOKYO</t>
+          <t>TIARA</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -38084,7 +38080,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>gelato pique</t>
+          <t>COCO DEAL</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -38107,7 +38103,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>TIARA</t>
+          <t>IÉNA</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -38130,7 +38126,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>COCO DEAL</t>
+          <t>SLOBE IÉNA</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -38153,7 +38149,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>IÉNA</t>
+          <t>Shinzone</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -38176,7 +38172,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>SLOBE IÉNA</t>
+          <t>Spick &amp; Span</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -38199,7 +38195,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Shinzone</t>
+          <t>STUDIOUS WOMENS</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -38222,7 +38218,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Spick &amp; Span</t>
+          <t>CLANE</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -38245,7 +38241,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>STUDIOUS WOMENS</t>
+          <t>JILL by JILL STUART</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -38268,7 +38264,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>CLANE</t>
+          <t>FREE'S MART</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -38291,7 +38287,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>JILL by JILL STUART</t>
+          <t>archives</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -38314,7 +38310,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>FREE'S MART</t>
+          <t>MERCURYDUO</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -38337,7 +38333,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>archives</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -38360,7 +38356,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>MERCURYDUO</t>
+          <t>LOWRYS FARM</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -38383,7 +38379,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Ungrid</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -38406,7 +38402,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>LOWRYS FARM</t>
+          <t>AndCouture</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -38429,7 +38425,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Ungrid</t>
+          <t>evelyn</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -38452,7 +38448,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>AndCouture</t>
+          <t>mystic</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -38475,7 +38471,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>evelyn</t>
+          <t>MURUA</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -38498,7 +38494,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>mystic</t>
+          <t>Seemi. by NICE CLAUP</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -38521,7 +38517,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>MURUA</t>
+          <t>REDYAZEL</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -38544,7 +38540,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Seemi. by NICE CLAUP</t>
+          <t>MOUSSY</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -38567,7 +38563,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>REDYAZEL</t>
+          <t>EMODA</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -38590,7 +38586,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>MOUSSY</t>
+          <t>SLY</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -38613,7 +38609,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>EMODA</t>
+          <t>JEANASIS</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -38636,7 +38632,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>SLY</t>
+          <t>Kastane</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -38659,7 +38655,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>JEANASIS</t>
+          <t>SALON by Chico</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -38682,7 +38678,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Kastane</t>
+          <t>EDIFICE</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -38705,7 +38701,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>SALON by Chico</t>
+          <t>UNITED ARROWS</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -38728,7 +38724,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>EDIFICE</t>
+          <t>ビームス</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -38751,7 +38747,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>UNITED ARROWS</t>
+          <t>ユナイテッドトウキョウ</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -38774,7 +38770,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>ビームス</t>
+          <t>バブアー</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -38797,7 +38793,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>ユナイテッドトウキョウ</t>
+          <t>TOMORROWLAND</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -38820,7 +38816,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>バブアー</t>
+          <t>PUBLIC TOKYO</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -38843,7 +38839,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>TOMORROWLAND</t>
+          <t>URBAN RESEARCH</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -38866,7 +38862,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>PUBLIC TOKYO</t>
+          <t>ADAM ET ROPE</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -38889,7 +38885,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>URBAN RESEARCH</t>
+          <t>JOURNAL STANDARD</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -38912,7 +38908,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>ADAM ET ROPE</t>
+          <t>ユナイテッドアローズ グリーンレーベル リラクシング</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -38935,7 +38931,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>JOURNAL STANDARD</t>
+          <t>Traditional Weatherwear</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -38958,7 +38954,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>ユナイテッドアローズ グリーンレーベル リラクシング</t>
+          <t>OUTDOOR PRODUCTS USUALTHINGS</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -38981,7 +38977,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Traditional Weatherwear</t>
+          <t>Bshop</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -39004,7 +39000,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>OUTDOOR PRODUCTS USUALTHINGS</t>
+          <t>MHL,</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -39027,7 +39023,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Bshop</t>
+          <t>FREAK'S STORE</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -39050,7 +39046,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>MHL,</t>
+          <t>CITEN</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -39073,7 +39069,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>FREAK'S STORE</t>
+          <t>ジーユー</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -39096,7 +39092,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>CITEN</t>
+          <t>ピーチ・ジョン</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -39119,7 +39115,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>ジーユー</t>
+          <t>リサマリ</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -39142,7 +39138,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>ピーチ・ジョン</t>
+          <t>ante by intesucre</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -39165,7 +39161,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>リサマリ</t>
+          <t>San-ai Resort</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -39188,7 +39184,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>ante by intesucre</t>
+          <t>BALENCIAGA</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -39198,7 +39194,7 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E775" t="inlineStr"/>
@@ -39211,7 +39207,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>San-ai Resort</t>
+          <t>MONCLER</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -39221,7 +39217,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E776" t="inlineStr"/>
@@ -39234,7 +39230,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>BALENCIAGA</t>
+          <t>Gallery CABaN</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -39257,7 +39253,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>MONCLER</t>
+          <t>JOHN SMEDLEY</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -39280,7 +39276,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Gallery CABaN</t>
+          <t>MACKINTOSH</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -39303,7 +39299,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>JOHN SMEDLEY</t>
+          <t>THE TOKYO</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -39326,7 +39322,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>MACKINTOSH</t>
+          <t>Drawing Numbers</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -39349,7 +39345,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>THE TOKYO</t>
+          <t>BRITISH MADE</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -39372,7 +39368,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Drawing Numbers</t>
+          <t>LOVELESS</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -39395,7 +39391,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>BRITISH MADE</t>
+          <t>evam eva</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -39418,7 +39414,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>LOVELESS</t>
+          <t>DESCENTE</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -39441,7 +39437,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>evam eva</t>
+          <t>SeeP EYEVAN</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -39464,7 +39460,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>DESCENTE</t>
+          <t>A.P.C.</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -39487,7 +39483,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>SeeP EYEVAN</t>
+          <t>MARGARET HOWELL</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -39510,7 +39506,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>A.P.C.</t>
+          <t>CABaN</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -39533,7 +39529,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>MARGARET HOWELL</t>
+          <t>agnès b.</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -39556,7 +39552,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>CABaN</t>
+          <t>Steven Alan</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -39579,7 +39575,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>agnès b.</t>
+          <t>ANATOMICA</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -39602,7 +39598,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Steven Alan</t>
+          <t>MAISON KITSUNÉ</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -39625,7 +39621,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>ANATOMICA</t>
+          <t>GALERIE VIE</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -39648,7 +39644,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>MAISON KITSUNÉ</t>
+          <t>Polo Ralph Lauren</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -39671,7 +39667,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>GALERIE VIE</t>
+          <t>Edit united arrows</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -39694,7 +39690,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Polo Ralph Lauren</t>
+          <t>yuni</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -39717,7 +39713,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Edit united arrows</t>
+          <t>MARcourt DESIGNEYE</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -39740,7 +39736,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>yuni</t>
+          <t>Sea Room lynn</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -39763,7 +39759,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>MARcourt DESIGNEYE</t>
+          <t>Whim Gazette</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -39786,7 +39782,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Sea Room lynn</t>
+          <t>1er Arrondissement</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -39809,7 +39805,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Whim Gazette</t>
+          <t>Curensology</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -39832,7 +39828,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>1er Arrondissement</t>
+          <t>MAISON SPECIAL WOMENS</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -39855,7 +39851,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Curensology</t>
+          <t>OUR WACOAL</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -39878,7 +39874,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>MAISON SPECIAL WOMENS</t>
+          <t>PRANK PROJECT</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -39901,7 +39897,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>OUR WACOAL</t>
+          <t>LE PHIL</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -39924,7 +39920,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>PRANK PROJECT</t>
+          <t>AP STUDIO</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -39947,7 +39943,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>LE PHIL</t>
+          <t>ESTNATION</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -39970,7 +39966,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>AP STUDIO</t>
+          <t>Chaos</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -39993,7 +39989,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>ESTNATION</t>
+          <t>BRILL</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -40016,7 +40012,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Chaos</t>
+          <t>オオカミとフクロウ</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -40039,7 +40035,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>BRILL</t>
+          <t>3(march)（THE NORTH FACE）</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -40062,7 +40058,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>オオカミとフクロウ</t>
+          <t>MAISON SPECIAL MENS</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -40085,7 +40081,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>3(march)（THE NORTH FACE）</t>
+          <t>YANUK</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -40108,7 +40104,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>MAISON SPECIAL MENS</t>
+          <t>無印良品</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -40131,7 +40127,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>YANUK</t>
+          <t>TENERITA</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -40154,7 +40150,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>無印良品</t>
+          <t>EMILY WEEK</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -40177,7 +40173,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>TENERITA</t>
+          <t>WWS</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -40200,7 +40196,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EMILY WEEK</t>
+          <t>RAGTAG</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -40223,7 +40219,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>WWS</t>
+          <t>ALBOVE・PEAK＆PINE</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -40241,22 +40237,22 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>衣料</t>
+          <t>酒</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>RAGTAG</t>
+          <t>セゾンファクトリー</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E821" t="inlineStr"/>
@@ -40264,22 +40260,22 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>衣料</t>
+          <t>酒</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>ALBOVE・PEAK＆PINE</t>
+          <t>ヴィノスやまざき</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E822" t="inlineStr"/>
@@ -40292,7 +40288,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>セゾンファクトリー</t>
+          <t>オリーヴォ</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -40315,7 +40311,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>ヴィノスやまざき</t>
+          <t>サカナバッカ</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -40338,20 +40334,24 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>オリーヴォ</t>
+          <t>成城石井</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E825" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -40361,20 +40361,24 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>サカナバッカ</t>
+          <t>PXストア</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E826" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -40384,7 +40388,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>成城石井</t>
+          <t>自然食品F&amp;F</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -40411,7 +40415,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>PXストア</t>
+          <t>ワイズマート</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -40438,7 +40442,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>自然食品F&amp;F</t>
+          <t>魚力</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -40465,7 +40469,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>ワイズマート</t>
+          <t>ニュー・クイック</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -40492,7 +40496,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>魚力</t>
+          <t>さわみつ青果</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -40519,7 +40523,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>ニュー・クイック</t>
+          <t>金子園</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -40546,7 +40550,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>さわみつ青果</t>
+          <t>茶 丸山園</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -40573,7 +40577,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>金子園</t>
+          <t>大川水産</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
@@ -40600,7 +40604,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>茶 丸山園</t>
+          <t>成城石井</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -40615,7 +40619,7 @@
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -40627,7 +40631,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>大川水産</t>
+          <t>ザ フルーツ ショップ</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -40642,7 +40646,7 @@
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -40654,7 +40658,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>成城石井</t>
+          <t>ふるまいや（日本酒）</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -40669,7 +40673,7 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -40681,24 +40685,20 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>ザ フルーツ ショップ</t>
+          <t>成城石井</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E838" t="inlineStr">
-        <is>
-          <t>3F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -40708,24 +40708,20 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>ふるまいや（日本酒）</t>
+          <t>カルディコーヒーファーム</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E839" t="inlineStr">
-        <is>
-          <t>3F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -40735,7 +40731,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>成城石井</t>
+          <t>AKOMEYA TOKYO</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -40745,7 +40741,7 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E840" t="inlineStr"/>
@@ -40758,7 +40754,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>カルディコーヒーファーム</t>
+          <t>ヴィノスやまざき</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -40768,7 +40764,7 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E841" t="inlineStr"/>
@@ -40781,7 +40777,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>AKOMEYA TOKYO</t>
+          <t>DEAN ＆ DELUCA</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -40804,7 +40800,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>ヴィノスやまざき</t>
+          <t>魚の北辰</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -40827,7 +40823,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>DEAN ＆ DELUCA</t>
+          <t>Daily Table KINOKUNIYA</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -40850,7 +40846,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>魚の北辰</t>
+          <t>ニュー・クイック</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -40873,7 +40869,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Daily Table KINOKUNIYA</t>
+          <t>九州屋</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -40896,7 +40892,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>ニュー・クイック</t>
+          <t>大川水産</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -40919,7 +40915,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>九州屋</t>
+          <t>文化堂</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -40929,7 +40925,7 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>CIAL横浜ANNEX</t>
         </is>
       </c>
       <c r="E848" t="inlineStr"/>
@@ -40942,7 +40938,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>大川水産</t>
+          <t>三河屋</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -40952,7 +40948,7 @@
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>CIAL横浜ANNEX</t>
         </is>
       </c>
       <c r="E849" t="inlineStr"/>
@@ -40960,22 +40956,22 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>酒</t>
+          <t>靴</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>文化堂</t>
+          <t>ヴィド-ポッシュ ドゥ セピカ</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>CIAL横浜ANNEX</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E850" t="inlineStr"/>
@@ -40983,22 +40979,22 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>酒</t>
+          <t>靴</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>三河屋</t>
+          <t>RANDA</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>CIAL横浜ANNEX</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E851" t="inlineStr"/>
@@ -41011,20 +41007,24 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>ヴィド-ポッシュ ドゥ セピカ</t>
+          <t>リリアンカラット</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
-        </is>
-      </c>
-      <c r="E852" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -41034,20 +41034,24 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>RANDA</t>
+          <t>ラシット</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -41057,7 +41061,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>リリアンカラット</t>
+          <t>ハートダンス</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -41072,7 +41076,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -41084,7 +41088,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>ラシット</t>
+          <t>WORK STYLE BEAUTIES</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -41099,7 +41103,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -41111,7 +41115,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>ハートダンス</t>
+          <t>ダイアナ</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -41126,7 +41130,7 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -41138,7 +41142,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>WORK STYLE BEAUTIES</t>
+          <t>レスポートサック</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -41153,7 +41157,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -41165,7 +41169,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>ダイアナ</t>
+          <t>ジュエッテ</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -41192,7 +41196,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>レスポートサック</t>
+          <t>テイクアップアウラ</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -41219,7 +41223,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>ジュエッテ</t>
+          <t>アクセサリーズブラッサム</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -41246,7 +41250,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>テイクアップアウラ</t>
+          <t>イアパピヨネ</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -41273,7 +41277,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>アクセサリーズブラッサム</t>
+          <t>ドロワーズ マイ フェヴァリット</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -41300,7 +41304,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>イアパピヨネ</t>
+          <t>靴下屋</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -41327,7 +41331,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>ドロワーズ マイ フェヴァリット</t>
+          <t>オリエンタルトラフィック</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -41342,7 +41346,7 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>4F</t>
         </is>
       </c>
     </row>
@@ -41354,7 +41358,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>靴下屋</t>
+          <t>ABCマート</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -41369,7 +41373,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>6F</t>
         </is>
       </c>
     </row>
@@ -41381,24 +41385,20 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>オリエンタルトラフィック</t>
+          <t>DÉCOUVERTE</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E866" t="inlineStr">
-        <is>
-          <t>4F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -41408,24 +41408,20 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>ABCマート</t>
+          <t>e.m.</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E867" t="inlineStr">
-        <is>
-          <t>6F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -41435,7 +41431,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>DÉCOUVERTE</t>
+          <t>agete</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -41458,7 +41454,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>e.m.</t>
+          <t>STAR JEWELRY</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -41481,7 +41477,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>agete</t>
+          <t>cui-cui</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -41504,7 +41500,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>STAR JEWELRY</t>
+          <t>Jouete</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -41527,7 +41523,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>cui-cui</t>
+          <t>ete</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -41550,7 +41546,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Jouete</t>
+          <t>AIMER</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -41573,7 +41569,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>ete</t>
+          <t>GOLDY</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -41596,7 +41592,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>AIMER</t>
+          <t>HIROB</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -41619,7 +41615,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>GOLDY</t>
+          <t>REPOS russet</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -41642,7 +41638,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>HIROB</t>
+          <t>Samantha Thavasa</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -41665,7 +41661,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>REPOS russet</t>
+          <t>LE TALON</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -41688,7 +41684,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Samantha Thavasa</t>
+          <t>DIANA</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -41711,7 +41707,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>LE TALON</t>
+          <t>BIRKENSTOCK</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -41734,7 +41730,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>DIANA</t>
+          <t>ORiental TRaffic</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -41757,7 +41753,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>BIRKENSTOCK</t>
+          <t>WASH</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -41780,7 +41776,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>ORiental TRaffic</t>
+          <t>Re:See</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -41803,7 +41799,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>WASH</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -41826,7 +41822,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Re:See</t>
+          <t>靴下屋</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -41849,7 +41845,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>because</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -41872,7 +41868,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>靴下屋</t>
+          <t>ANEMONE</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -41895,7 +41891,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>because</t>
+          <t>トポロジー</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -41918,7 +41914,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>ANEMONE</t>
+          <t>Tiffany &amp; Co.</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -41928,7 +41924,7 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E889" t="inlineStr"/>
@@ -41941,7 +41937,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>トポロジー</t>
+          <t>UGG</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -41951,7 +41947,7 @@
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E890" t="inlineStr"/>
@@ -41964,7 +41960,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Tiffany &amp; Co.</t>
+          <t>KURA CHIKA by PORTER</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -41987,7 +41983,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>UGG</t>
+          <t>Dr.Martens</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -42010,7 +42006,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>KURA CHIKA by PORTER</t>
+          <t>Maker's Watch Knot</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -42033,7 +42029,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Dr.Martens</t>
+          <t>'eir</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -42056,7 +42052,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Maker's Watch Knot</t>
+          <t>BLANC IRIS</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -42079,7 +42075,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>'eir</t>
+          <t>designsix</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -42102,7 +42098,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>BLANC IRIS</t>
+          <t>Jouete L/</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -42125,7 +42121,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>designsix</t>
+          <t>BIZOUX</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -42148,7 +42144,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Jouete L/</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -42171,7 +42167,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>BIZOUX</t>
+          <t>Tabio</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -42194,7 +42190,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>LONGCHAMP</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -42217,7 +42213,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>Tabio</t>
+          <t>SLOW authentic goods store</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -42235,22 +42231,22 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>靴</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>LONGCHAMP</t>
+          <t>ディーン＆デルーカ</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E903" t="inlineStr"/>
@@ -42258,22 +42254,22 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>靴</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>SLOW authentic goods store</t>
+          <t>中川政七商店</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E904" t="inlineStr"/>
@@ -42286,7 +42282,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>ディーン＆デルーカ</t>
+          <t>FOOD＆TIME ISETAN</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
@@ -42309,7 +42305,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>中川政七商店</t>
+          <t>QUEEN'S ISETAN</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
@@ -42332,7 +42328,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>FOOD＆TIME ISETAN</t>
+          <t>セゾンファクトリー</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
@@ -42342,7 +42338,7 @@
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E907" t="inlineStr"/>
@@ -42355,7 +42351,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>QUEEN'S ISETAN</t>
+          <t>ヴィノスやまざき</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -42365,7 +42361,7 @@
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E908" t="inlineStr"/>
@@ -42378,7 +42374,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>セゾンファクトリー</t>
+          <t>オリーヴォ</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -42401,7 +42397,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>ヴィノスやまざき</t>
+          <t>サカナバッカ</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
@@ -42424,20 +42420,24 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>オリーヴォ</t>
+          <t>成城石井</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E911" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -42447,20 +42447,24 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>サカナバッカ</t>
+          <t>PXストア</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E912" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -42470,7 +42474,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>成城石井</t>
+          <t>自然食品F&amp;F</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -42497,7 +42501,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>PXストア</t>
+          <t>ワイズマート</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
@@ -42524,7 +42528,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>自然食品F&amp;F</t>
+          <t>魚力</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
@@ -42551,7 +42555,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>ワイズマート</t>
+          <t>ニュー・クイック</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -42578,7 +42582,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>魚力</t>
+          <t>さわみつ青果</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
@@ -42605,7 +42609,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>ニュー・クイック</t>
+          <t>金子園</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
@@ -42632,7 +42636,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>さわみつ青果</t>
+          <t>茶 丸山園</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
@@ -42659,7 +42663,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>金子園</t>
+          <t>大川水産</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
@@ -42686,7 +42690,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>茶 丸山園</t>
+          <t>成城石井</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -42701,7 +42705,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -42713,7 +42717,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>大川水産</t>
+          <t>ザ フルーツ ショップ</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -42728,7 +42732,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -42740,7 +42744,7 @@
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>成城石井</t>
+          <t>ふるまいや（日本酒）</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
@@ -42755,7 +42759,7 @@
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -42767,24 +42771,20 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>ザ フルーツ ショップ</t>
+          <t>成城石井</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E924" t="inlineStr">
-        <is>
-          <t>3F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr"/>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -42794,24 +42794,20 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>ふるまいや（日本酒）</t>
+          <t>カルディコーヒーファーム</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E925" t="inlineStr">
-        <is>
-          <t>3F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr"/>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -42821,24 +42817,20 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>無印良品</t>
+          <t>中川政七商店</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E926" t="inlineStr">
-        <is>
-          <t>4F</t>
-        </is>
-      </c>
+          <t>ルミネ横浜</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr"/>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -42848,7 +42840,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>成城石井</t>
+          <t>AKOMEYA TOKYO</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -42858,7 +42850,7 @@
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E927" t="inlineStr"/>
@@ -42871,7 +42863,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>カルディコーヒーファーム</t>
+          <t>ヴィノスやまざき</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -42881,7 +42873,7 @@
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E928" t="inlineStr"/>
@@ -42894,7 +42886,7 @@
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>中川政七商店</t>
+          <t>DEAN ＆ DELUCA</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
@@ -42904,7 +42896,7 @@
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E929" t="inlineStr"/>
@@ -42917,7 +42909,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>無印良品</t>
+          <t>魚の北辰</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
@@ -42927,7 +42919,7 @@
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E930" t="inlineStr"/>
@@ -42940,7 +42932,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>AKOMEYA TOKYO</t>
+          <t>Daily Table KINOKUNIYA</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -42963,7 +42955,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>ヴィノスやまざき</t>
+          <t>ニュー・クイック</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -42986,7 +42978,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>DEAN ＆ DELUCA</t>
+          <t>九州屋</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -43009,7 +43001,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>魚の北辰</t>
+          <t>大川水産</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -43032,7 +43024,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Daily Table KINOKUNIYA</t>
+          <t>文化堂</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -43042,7 +43034,7 @@
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>CIAL横浜ANNEX</t>
         </is>
       </c>
       <c r="E935" t="inlineStr"/>
@@ -43055,7 +43047,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>ニュー・クイック</t>
+          <t>三河屋</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -43065,7 +43057,7 @@
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>CIAL横浜ANNEX</t>
         </is>
       </c>
       <c r="E936" t="inlineStr"/>
@@ -43073,117 +43065,25 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>駅ナカ全般</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>九州屋</t>
+          <t>エキュート品川内 JRE POINTマーク対象ショップ</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E937" t="inlineStr"/>
-    </row>
-    <row r="938">
-      <c r="A938" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B938" t="inlineStr">
-        <is>
-          <t>大川水産</t>
-        </is>
-      </c>
-      <c r="C938" t="inlineStr">
-        <is>
-          <t>横浜</t>
-        </is>
-      </c>
-      <c r="D938" t="inlineStr">
-        <is>
-          <t>CIAL横浜</t>
-        </is>
-      </c>
-      <c r="E938" t="inlineStr"/>
-    </row>
-    <row r="939">
-      <c r="A939" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B939" t="inlineStr">
-        <is>
-          <t>文化堂</t>
-        </is>
-      </c>
-      <c r="C939" t="inlineStr">
-        <is>
-          <t>横浜</t>
-        </is>
-      </c>
-      <c r="D939" t="inlineStr">
-        <is>
-          <t>CIAL横浜ANNEX</t>
-        </is>
-      </c>
-      <c r="E939" t="inlineStr"/>
-    </row>
-    <row r="940">
-      <c r="A940" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B940" t="inlineStr">
-        <is>
-          <t>三河屋</t>
-        </is>
-      </c>
-      <c r="C940" t="inlineStr">
-        <is>
-          <t>横浜</t>
-        </is>
-      </c>
-      <c r="D940" t="inlineStr">
-        <is>
-          <t>CIAL横浜ANNEX</t>
-        </is>
-      </c>
-      <c r="E940" t="inlineStr"/>
-    </row>
-    <row r="941">
-      <c r="A941" t="inlineStr">
-        <is>
-          <t>駅ナカ全般</t>
-        </is>
-      </c>
-      <c r="B941" t="inlineStr">
-        <is>
-          <t>エキュート品川内 JRE POINTマーク対象ショップ</t>
-        </is>
-      </c>
-      <c r="C941" t="inlineStr">
-        <is>
-          <t>品川</t>
-        </is>
-      </c>
-      <c r="D941" t="inlineStr">
-        <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E941" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JREポイント完全データベース_統合版_v5.xlsx
+++ b/JREポイント完全データベース_統合版_v5.xlsx
@@ -5776,7 +5776,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>キッズ</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>キッズ</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>キッズ</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -21608,35 +21608,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ギフト</t>
+          <t>キッズ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>青山フラワーマーケット</t>
+          <t>TAKUJI STATION</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ギフト</t>
+          <t>キッズ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>モンソー フルール</t>
+          <t>めばえ教室</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -21651,19 +21655,19 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>7F</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ギフト</t>
+          <t>キッズ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>青山フラワーマーケット</t>
+          <t>ミキハウスキッズパル</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -21678,7 +21682,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>7F</t>
         </is>
       </c>
     </row>
@@ -21690,24 +21694,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>アフタヌーンティー・ギフト&amp;リビング</t>
+          <t>青山フラワーマーケット</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>3F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -21717,7 +21717,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>バースデイ・バー</t>
+          <t>モンソー フルール</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -21744,7 +21744,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>青山フラワーマーケット ミドリギゲート店</t>
+          <t>青山フラワーマーケット</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -21771,20 +21771,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>フルラージュアン</t>
+          <t>アフタヌーンティー・ギフト&amp;リビング</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -21794,20 +21798,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BIRTHDAY BAR</t>
+          <t>バースデイ・バー</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -21817,40 +21825,44 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FLEURISTE BON MARCHE</t>
+          <t>青山フラワーマーケット ミドリギゲート店</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>コスメ</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AP by AMERICAN PHARMACY</t>
+          <t>フルラージュアン</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -21858,22 +21870,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>コスメ</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>フルーツギャザリング</t>
+          <t>BIRTHDAY BAR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -21881,29 +21893,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>コスメ</t>
+          <t>ギフト</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>エンハーブ</t>
+          <t>FLEURISTE BON MARCHE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
+          <t>CIAL横浜</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -21913,24 +21921,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ザボディショップ</t>
+          <t>AP by AMERICAN PHARMACY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
+          <t>アトレ品川</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -21940,24 +21944,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>トモズ</t>
+          <t>フルーツギャザリング</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -21967,7 +21967,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ファンケル</t>
+          <t>エンハーブ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ハウスオブローゼ</t>
+          <t>ザボディショップ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>オルビス</t>
+          <t>トモズ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -22048,7 +22048,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ラッシュ</t>
+          <t>ファンケル</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ビープル</t>
+          <t>ハウスオブローゼ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -22102,7 +22102,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ザ コスメティック テラス ブルーストライプ</t>
+          <t>オルビス</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -22117,7 +22117,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -22129,7 +22129,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>パウダーパレット/ビューズアイブロウスタジオ</t>
+          <t>ラッシュ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -22144,7 +22144,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>4F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22156,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>シャン・ド・エルブ</t>
+          <t>ビープル</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>4F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -22183,20 +22183,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>@cosme STORE</t>
+          <t>ザ コスメティック テラス ブルーストライプ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -22206,20 +22210,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CHANEL FRAGRANCE&amp;BEAUTY</t>
+          <t>パウダーパレット/ビューズアイブロウスタジオ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>4F</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -22229,20 +22237,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Aesop</t>
+          <t>シャン・ド・エルブ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>4F</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -22252,7 +22264,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>キールズ</t>
+          <t>@cosme STORE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -22275,7 +22287,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IPSA</t>
+          <t>CHANEL FRAGRANCE&amp;BEAUTY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -22298,7 +22310,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>Aesop</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -22321,7 +22333,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SABON</t>
+          <t>キールズ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -22344,7 +22356,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SHIRO</t>
+          <t>IPSA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -22367,7 +22379,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ORBIS</t>
+          <t>track</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -22390,7 +22402,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Leafie</t>
+          <t>SABON</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -22413,7 +22425,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>マークスアンドウェブ</t>
+          <t>SHIRO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -22436,7 +22448,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OSAJI</t>
+          <t>ORBIS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -22459,7 +22471,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MUCHA</t>
+          <t>Leafie</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -22482,7 +22494,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The PERFUME OIL FACTORY</t>
+          <t>マークスアンドウェブ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -22505,7 +22517,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>OSAJI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -22528,7 +22540,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Aiam</t>
+          <t>MUCHA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -22551,7 +22563,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AUX PARADIS</t>
+          <t>The PERFUME OIL FACTORY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -22574,7 +22586,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cosme Kitchen</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -22597,7 +22609,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>enherb</t>
+          <t>Aiam</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -22620,7 +22632,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ジョンマスターオーガニック</t>
+          <t>AUX PARADIS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -22643,7 +22655,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OFFICINE UNIVERSELLE BULY</t>
+          <t>Cosme Kitchen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -22653,7 +22665,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -22666,7 +22678,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dior BACKSTAGE STUDIO</t>
+          <t>enherb</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -22676,7 +22688,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -22689,7 +22701,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>@cosme STORE</t>
+          <t>ジョンマスターオーガニック</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -22699,7 +22711,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -22712,7 +22724,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ALBION PHILOSOPHY</t>
+          <t>OFFICINE UNIVERSELLE BULY</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -22735,7 +22747,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>POLA</t>
+          <t>Dior BACKSTAGE STUDIO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -22758,7 +22770,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BAUM</t>
+          <t>@cosme STORE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -22781,7 +22793,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>uka store</t>
+          <t>ALBION PHILOSOPHY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -22804,7 +22816,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>北麓草水</t>
+          <t>POLA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -22827,7 +22839,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Aēsop</t>
+          <t>BAUM</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -22850,7 +22862,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LE LABO</t>
+          <t>uka store</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -22873,7 +22885,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DIPTYQUE</t>
+          <t>北麓草水</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -22896,7 +22908,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Santa Maria Novella</t>
+          <t>Aēsop</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -22919,7 +22931,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Maison Margiela Fragrances</t>
+          <t>LE LABO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -22942,7 +22954,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>APFR</t>
+          <t>DIPTYQUE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -22965,7 +22977,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NOSE SHOP</t>
+          <t>Santa Maria Novella</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -22988,7 +23000,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NOWHERE NOWHERE</t>
+          <t>Maison Margiela Fragrances</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -23011,7 +23023,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>@aroma</t>
+          <t>APFR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -23034,7 +23046,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>davines</t>
+          <t>NOSE SHOP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -23057,7 +23069,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ReFa</t>
+          <t>NOWHERE NOWHERE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -23075,22 +23087,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>コンビニ</t>
+          <t>コスメ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ニューデイズ キオスク</t>
+          <t>@aroma</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -23098,22 +23110,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>コンビニ</t>
+          <t>コスメ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ニューデイズ エキュート品川</t>
+          <t>davines</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -23121,29 +23133,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>コンビニ</t>
+          <t>コスメ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ニューデイズ</t>
+          <t>ReFa</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>北側改札内3F</t>
-        </is>
-      </c>
+          <t>ニュウマン横浜</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -23153,24 +23161,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ニューデイズ</t>
+          <t>ニューデイズ キオスク</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>3F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -23180,17 +23184,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NewDays</t>
+          <t>ニューデイズ エキュート品川</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>エキュート品川</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -23198,35 +23202,39 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>コンビニ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ミスターミニット</t>
+          <t>ニューデイズ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>北側改札内3F</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>コンビニ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>カメラのキタムラ</t>
+          <t>ニューデイズ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -23241,19 +23249,19 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>B1F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>コンビニ</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>お直しコンシェルジュ ビック・ママ</t>
+          <t>NewDays</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -23263,7 +23271,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -23276,17 +23284,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ピノキオ</t>
+          <t>ミスターミニット</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -23299,20 +23307,24 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>朝日カルチャーセンター</t>
+          <t>カメラのキタムラ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>B1F</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -23322,7 +23334,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Form-i</t>
+          <t>お直しコンシェルジュ ビック・ママ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -23332,7 +23344,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -23345,7 +23357,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MISTER MINIT</t>
+          <t>ピノキオ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -23355,7 +23367,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -23368,7 +23380,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>KOMEHYO買取センター</t>
+          <t>朝日カルチャーセンター</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -23378,7 +23390,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -23391,7 +23403,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NEWoMan Lab.</t>
+          <t>Form-i</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -23414,7 +23426,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NEWoMan Lab. petit</t>
+          <t>MISTER MINIT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -23437,7 +23449,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>STATION DESK横浜</t>
+          <t>KOMEHYO買取センター</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -23447,7 +23459,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>エキュートエディション横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -23455,22 +23467,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>スイーツ</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ディーン＆デルーカ</t>
+          <t>NEWoMan Lab.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -23478,22 +23490,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>スイーツ</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ゴディバ</t>
+          <t>NEWoMan Lab. petit</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -23501,22 +23513,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>スイーツ</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ピエール・エルメ・パリ</t>
+          <t>STATION DESK横浜</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>エキュートエディション横浜</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -23529,7 +23541,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>和楽紅屋</t>
+          <t>ディーン＆デルーカ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -23539,7 +23551,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -23552,7 +23564,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ふるや古賀音庵</t>
+          <t>ゴディバ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -23562,7 +23574,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -23575,7 +23587,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>自由が丘 蜂の家</t>
+          <t>ピエール・エルメ・パリ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -23585,7 +23597,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -23598,7 +23610,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>トップス</t>
+          <t>和楽紅屋</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -23621,7 +23633,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ダロワイヨ</t>
+          <t>ふるや古賀音庵</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -23644,7 +23656,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>御門屋</t>
+          <t>自由が丘 蜂の家</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -23667,7 +23679,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>パティスリー QBG</t>
+          <t>トップス</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -23690,7 +23702,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>空いろ</t>
+          <t>ダロワイヨ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -23713,7 +23725,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>アトリエうかい</t>
+          <t>御門屋</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -23736,7 +23748,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>銀座甘楽</t>
+          <t>パティスリー QBG</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -23759,7 +23771,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>菓匠三全</t>
+          <t>空いろ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -23782,7 +23794,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>マイスターシュトュック ユーハイム</t>
+          <t>アトリエうかい</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -23805,7 +23817,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>フェルム ラ・テール 美瑛</t>
+          <t>銀座甘楽</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -23828,7 +23840,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FiOLATTE/フィオラッテ</t>
+          <t>菓匠三全</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -23851,7 +23863,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HANAGATAYA</t>
+          <t>マイスターシュトュック ユーハイム</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -23874,7 +23886,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>京橋千疋屋</t>
+          <t>フェルム ラ・テール 美瑛</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -23897,7 +23909,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ヨックモック</t>
+          <t>FiOLATTE/フィオラッテ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -23920,7 +23932,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>柿の木坂 キャトル</t>
+          <t>HANAGATAYA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -23943,7 +23955,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>八天堂</t>
+          <t>京橋千疋屋</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -23966,7 +23978,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ねんりん家</t>
+          <t>ヨックモック</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -23989,7 +24001,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>鎌倉 豊島屋</t>
+          <t>柿の木坂 キャトル</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -24012,7 +24024,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>coneri 品川</t>
+          <t>八天堂</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -24035,7 +24047,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GOOD NEWS TOKYO</t>
+          <t>ねんりん家</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -24058,7 +24070,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>立町カヌレ SHINAGAWA</t>
+          <t>鎌倉 豊島屋</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -24081,7 +24093,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>VERY RUBY CUT</t>
+          <t>coneri 品川</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -24104,7 +24116,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>アンテノール Favorite Sweets</t>
+          <t>GOOD NEWS TOKYO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -24127,7 +24139,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ダンデライオン チョコレート</t>
+          <t>立町カヌレ SHINAGAWA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -24150,7 +24162,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>VERY RUBY CUT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -24173,7 +24185,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>I LOVE CUSTARD NEUFNEUF</t>
+          <t>アンテノール Favorite Sweets</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -24196,7 +24208,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dessert CHOUX</t>
+          <t>ダンデライオン チョコレート</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -24219,7 +24231,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>小樽洋菓子舗ルタオ</t>
+          <t>Recipe</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -24242,7 +24254,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BELTZ</t>
+          <t>I LOVE CUSTARD NEUFNEUF</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -24265,24 +24277,20 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>アントステラ</t>
+          <t>Dessert CHOUX</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -24292,24 +24300,20 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ゴディバ</t>
+          <t>小樽洋菓子舗ルタオ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -24319,24 +24323,20 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>フロ プレステージュ</t>
+          <t>BELTZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -24346,7 +24346,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>不二家</t>
+          <t>アントステラ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>東京凮月堂</t>
+          <t>ゴディバ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>文明堂</t>
+          <t>フロ プレステージュ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>フーシェ/尾張松風屋</t>
+          <t>不二家</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>浅草梅園</t>
+          <t>東京凮月堂</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>クリスピー・クリーム・ドーナツ</t>
+          <t>文明堂</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -24496,7 +24496,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -24508,7 +24508,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>柿の木坂キャトル</t>
+          <t>フーシェ/尾張松風屋</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ラップドクレープコロット</t>
+          <t>浅草梅園</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>りんごとバター。苺のワルツ</t>
+          <t>クリスピー・クリーム・ドーナツ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>クリスピー・クリーム・ドーナツ</t>
+          <t>柿の木坂キャトル</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24616,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>堂本</t>
+          <t>ラップドクレープコロット</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -24643,7 +24643,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>サーティワンアイスクリーム</t>
+          <t>りんごとバター。苺のワルツ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -24670,20 +24670,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JACK IN THE DONUTS</t>
+          <t>クリスピー・クリーム・ドーナツ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -24693,20 +24697,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ミスターワッフル</t>
+          <t>堂本</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -24716,20 +24724,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MAISON CACAO</t>
+          <t>サーティワンアイスクリーム</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -24739,7 +24751,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>スコーン専門店iro</t>
+          <t>JACK IN THE DONUTS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -24749,7 +24761,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -24762,7 +24774,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GRANNY SMITH APPLE PIE &amp; COFFEE</t>
+          <t>ミスターワッフル</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -24772,7 +24784,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -24785,7 +24797,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ありあけ本館 HARBOUR'S MOON</t>
+          <t>MAISON CACAO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -24795,7 +24807,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -24808,7 +24820,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>BLUE CACAO</t>
+          <t>スコーン専門店iro</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -24831,7 +24843,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ガトー・ド・ボワイヤージュ</t>
+          <t>GRANNY SMITH APPLE PIE &amp; COFFEE</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -24854,7 +24866,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ミサキドーナツ</t>
+          <t>ありあけ本館 HARBOUR'S MOON</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -24877,7 +24889,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ben's Cookies</t>
+          <t>BLUE CACAO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -24900,7 +24912,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ギャレット ポップコーン ショップス</t>
+          <t>ガトー・ド・ボワイヤージュ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -24923,7 +24935,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>湘南クリエイティブ・ガトー 葦</t>
+          <t>ミサキドーナツ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -24946,7 +24958,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>十勝あんこのサザエ</t>
+          <t>Ben's Cookies</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -24964,22 +24976,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>スーパー</t>
+          <t>スイーツ</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FOOD＆TIME ISETAN</t>
+          <t>ギャレット ポップコーン ショップス</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -24987,22 +24999,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>スーパー</t>
+          <t>スイーツ</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>QUEEN'S ISETAN</t>
+          <t>湘南クリエイティブ・ガトー 葦</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -25010,22 +25022,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>スーパー</t>
+          <t>スイーツ</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>セゾンファクトリー</t>
+          <t>十勝あんこのサザエ</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -25038,7 +25050,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ヴィノスやまざき</t>
+          <t>FOOD＆TIME ISETAN</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -25048,7 +25060,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -25061,7 +25073,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>オリーヴォ</t>
+          <t>QUEEN'S ISETAN</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -25071,7 +25083,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -25084,7 +25096,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>サカナバッカ</t>
+          <t>セゾンファクトリー</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -25107,24 +25119,20 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>成城石井</t>
+          <t>ヴィノスやまざき</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -25134,24 +25142,20 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PXストア</t>
+          <t>オリーヴォ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -25161,24 +25165,20 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>自然食品F&amp;F</t>
+          <t>サカナバッカ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ワイズマート</t>
+          <t>成城石井</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -25215,7 +25215,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>魚力</t>
+          <t>PXストア</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -25242,7 +25242,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ニュー・クイック</t>
+          <t>自然食品F&amp;F</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>さわみつ青果</t>
+          <t>ワイズマート</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>金子園</t>
+          <t>魚力</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>茶 丸山園</t>
+          <t>ニュー・クイック</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>大川水産</t>
+          <t>さわみつ青果</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>成城石井</t>
+          <t>金子園</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -25392,7 +25392,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ザ フルーツ ショップ</t>
+          <t>茶 丸山園</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ふるまいや（日本酒）</t>
+          <t>大川水産</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -25463,15 +25463,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>北側改札内3F</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -25481,20 +25485,24 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>カルディコーヒーファーム</t>
+          <t>ザ フルーツ ショップ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -25504,20 +25512,24 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>AKOMEYA TOKYO</t>
+          <t>ふるまいや（日本酒）</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -25527,7 +25539,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ヴィノスやまざき</t>
+          <t>成城石井</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -25537,7 +25549,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -25550,7 +25562,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>DEAN ＆ DELUCA</t>
+          <t>カルディコーヒーファーム</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -25560,7 +25572,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -25573,7 +25585,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>魚の北辰</t>
+          <t>AKOMEYA TOKYO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -25596,7 +25608,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Daily Table KINOKUNIYA</t>
+          <t>ヴィノスやまざき</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -25619,7 +25631,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ニュー・クイック</t>
+          <t>DEAN ＆ DELUCA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -25642,7 +25654,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>九州屋</t>
+          <t>魚の北辰</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -25665,7 +25677,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>大川水産</t>
+          <t>Daily Table KINOKUNIYA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -25688,7 +25700,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>文化堂</t>
+          <t>ニュー・クイック</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -25698,7 +25710,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>CIAL横浜ANNEX</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -25711,7 +25723,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>三河屋</t>
+          <t>九州屋</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -25721,7 +25733,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>CIAL横浜ANNEX</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -25729,22 +25741,22 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>バッグ</t>
+          <t>スーパー</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ヴィド-ポッシュ ドゥ セピカ</t>
+          <t>大川水産</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -25752,22 +25764,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>バッグ</t>
+          <t>スーパー</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>イア パピヨネ</t>
+          <t>文化堂</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>CIAL横浜ANNEX</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -25775,22 +25787,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>バッグ</t>
+          <t>スーパー</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>RANDA</t>
+          <t>三河屋</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>CIAL横浜ANNEX</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -25803,7 +25815,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ポータースタンド</t>
+          <t>ヴィド-ポッシュ ドゥ セピカ</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -25813,7 +25825,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
@@ -25826,24 +25838,20 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>リリアンカラット</t>
+          <t>イア パピヨネ</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
+          <t>アトレ品川</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -25853,24 +25861,20 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ラシット</t>
+          <t>RANDA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
+          <t>アトレ品川</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -25880,24 +25884,20 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ハートダンス</t>
+          <t>ポータースタンド</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>2F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -25907,7 +25907,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>WORK STYLE BEAUTIES</t>
+          <t>リリアンカラット</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -25922,7 +25922,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ダイアナ</t>
+          <t>ラシット</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -25949,7 +25949,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -25961,7 +25961,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>レスポートサック</t>
+          <t>ハートダンス</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -25976,7 +25976,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -25988,7 +25988,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ジュエッテ</t>
+          <t>WORK STYLE BEAUTIES</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -26003,7 +26003,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>テイクアップアウラ</t>
+          <t>ダイアナ</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>アクセサリーズブラッサム</t>
+          <t>レスポートサック</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -26069,7 +26069,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>イアパピヨネ</t>
+          <t>ジュエッテ</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -26096,7 +26096,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ドロワーズ マイ フェヴァリット</t>
+          <t>テイクアップアウラ</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -26123,7 +26123,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>靴下屋</t>
+          <t>アクセサリーズブラッサム</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -26150,7 +26150,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>オリエンタルトラフィック</t>
+          <t>イアパピヨネ</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -26165,7 +26165,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>4F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -26177,7 +26177,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ABCマート</t>
+          <t>ドロワーズ マイ フェヴァリット</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -26192,7 +26192,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>6F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -26204,20 +26204,24 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DÉCOUVERTE</t>
+          <t>靴下屋</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -26227,20 +26231,24 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>e.m.</t>
+          <t>オリエンタルトラフィック</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>4F</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -26250,20 +26258,24 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>agete</t>
+          <t>ABCマート</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>6F</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -26273,7 +26285,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>STAR JEWELRY</t>
+          <t>DÉCOUVERTE</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -26296,7 +26308,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>cui-cui</t>
+          <t>e.m.</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -26319,7 +26331,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Jouete</t>
+          <t>agete</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -26342,7 +26354,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ete</t>
+          <t>STAR JEWELRY</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -26365,7 +26377,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>AIMER</t>
+          <t>cui-cui</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -26388,7 +26400,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>GOLDY</t>
+          <t>Jouete</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -26411,7 +26423,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>HIROB</t>
+          <t>ete</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -26434,7 +26446,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>REPOS russet</t>
+          <t>AIMER</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -26457,7 +26469,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Samantha Thavasa</t>
+          <t>GOLDY</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -26480,7 +26492,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>LE TALON</t>
+          <t>HIROB</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -26503,7 +26515,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DIANA</t>
+          <t>REPOS russet</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -26526,7 +26538,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>BIRKENSTOCK</t>
+          <t>Samantha Thavasa</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -26549,7 +26561,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ORiental TRaffic</t>
+          <t>LE TALON</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -26572,7 +26584,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>WASH</t>
+          <t>DIANA</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -26595,7 +26607,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Re:See</t>
+          <t>BIRKENSTOCK</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -26618,7 +26630,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>RIM</t>
+          <t>ORiental TRaffic</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -26641,7 +26653,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>靴下屋</t>
+          <t>WASH</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -26664,7 +26676,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>because</t>
+          <t>Re:See</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -26687,7 +26699,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ANEMONE</t>
+          <t>RIM</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -26710,7 +26722,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>トポロジー</t>
+          <t>靴下屋</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -26733,7 +26745,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>GREGORY</t>
+          <t>because</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -26756,7 +26768,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Tiffany &amp; Co.</t>
+          <t>ANEMONE</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -26766,7 +26778,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -26779,7 +26791,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>UGG</t>
+          <t>トポロジー</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -26789,7 +26801,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -26802,7 +26814,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>KURA CHIKA by PORTER</t>
+          <t>GREGORY</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -26812,7 +26824,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E265" t="inlineStr"/>
@@ -26825,7 +26837,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Dr.Martens</t>
+          <t>Tiffany &amp; Co.</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -26848,7 +26860,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Maker's Watch Knot</t>
+          <t>UGG</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -26871,7 +26883,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>'eir</t>
+          <t>KURA CHIKA by PORTER</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -26894,7 +26906,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>BLANC IRIS</t>
+          <t>Dr.Martens</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -26917,7 +26929,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>designsix</t>
+          <t>Maker's Watch Knot</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -26940,7 +26952,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Jouete L/</t>
+          <t>'eir</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -26963,7 +26975,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>BIZOUX</t>
+          <t>BLANC IRIS</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -26986,7 +26998,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>designsix</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -27009,7 +27021,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Tabio</t>
+          <t>Jouete L/</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -27032,7 +27044,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>LONGCHAMP</t>
+          <t>BIZOUX</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -27055,7 +27067,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SLOW authentic goods store</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -27073,22 +27085,22 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ベーカリー</t>
+          <t>バッグ</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>ザ シティ ベーカリー</t>
+          <t>Tabio</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -27096,22 +27108,22 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ベーカリー</t>
+          <t>バッグ</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>BLUE BOTTLE COFFEE</t>
+          <t>LONGCHAMP</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -27119,22 +27131,22 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ベーカリー</t>
+          <t>バッグ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>サンジェルマン</t>
+          <t>SLOW authentic goods store</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -27147,7 +27159,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>サザコーヒー</t>
+          <t>ザ シティ ベーカリー</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -27157,7 +27169,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -27170,7 +27182,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>ポール</t>
+          <t>BLUE BOTTLE COFFEE</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -27180,7 +27192,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -27193,7 +27205,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>加賀棒茶 丸八製茶場</t>
+          <t>サンジェルマン</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -27203,7 +27215,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -27216,7 +27228,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>常陸野ブルーイング品川</t>
+          <t>サザコーヒー</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -27239,7 +27251,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>アンデルセン</t>
+          <t>ポール</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -27262,7 +27274,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>タミルズ</t>
+          <t>加賀棒茶 丸八製茶場</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -27285,7 +27297,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>ヴェラーチェ パネッテリア-ガストロノミア</t>
+          <t>常陸野ブルーイング品川</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -27308,7 +27320,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>BOUL'ANGE</t>
+          <t>アンデルセン</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -27331,24 +27343,20 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>ノブ カフェ</t>
+          <t>タミルズ</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -27358,24 +27366,20 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>アンデルセン</t>
+          <t>ヴェラーチェ パネッテリア-ガストロノミア</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -27385,24 +27389,20 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>神戸屋キッチン エクスプレス</t>
+          <t>BOUL'ANGE</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>北側改札内3F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>スターバックスコーヒー</t>
+          <t>ノブ カフェ</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -27427,7 +27427,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -27439,7 +27439,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>デリフランス</t>
+          <t>アンデルセン</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -27466,7 +27466,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>タリーズコーヒー</t>
+          <t>神戸屋キッチン エクスプレス</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -27481,7 +27481,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -27493,7 +27493,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>アフタヌーンティー・ティールーム</t>
+          <t>スターバックスコーヒー</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -27508,7 +27508,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -27520,7 +27520,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>神戸屋キッチン エクスプレス</t>
+          <t>デリフランス</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -27535,7 +27535,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>スターバックスコーヒー</t>
+          <t>タリーズコーヒー</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -27562,7 +27562,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -27574,7 +27574,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ワイアードカフェ</t>
+          <t>アフタヌーンティー・ティールーム</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -27601,7 +27601,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>椿屋茶房</t>
+          <t>神戸屋キッチン エクスプレス</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -27616,7 +27616,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -27628,7 +27628,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ディーン アンド デルーカ</t>
+          <t>スターバックスコーヒー</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -27655,7 +27655,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>ポール</t>
+          <t>ワイアードカフェ</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -27682,7 +27682,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>コーヒーミルク</t>
+          <t>椿屋茶房</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -27709,7 +27709,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>ゴンチャ</t>
+          <t>ディーン アンド デルーカ</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -27736,20 +27736,24 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ブランジェ浅野屋</t>
+          <t>ポール</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -27759,20 +27763,24 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>HARBS</t>
+          <t>コーヒーミルク</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -27782,20 +27790,24 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>スターバックス</t>
+          <t>ゴンチャ</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -27805,7 +27817,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>24/7 coffee &amp; roaster</t>
+          <t>ブランジェ浅野屋</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -27828,7 +27840,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>アフタヌーンティー・ラブアンドテーブル</t>
+          <t>HARBS</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -27851,7 +27863,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>BLUE BOTTLE COFFEE</t>
+          <t>スターバックス</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -27861,7 +27873,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
@@ -27874,7 +27886,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>TULLY'S COFFEE</t>
+          <t>24/7 coffee &amp; roaster</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -27884,7 +27896,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
@@ -27897,7 +27909,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>SMITH TEAMAKER</t>
+          <t>アフタヌーンティー・ラブアンドテーブル</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -27907,7 +27919,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
@@ -27920,7 +27932,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ERIC ROSE YOKOHAMA COFFEE</t>
+          <t>BLUE BOTTLE COFFEE</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -27943,7 +27955,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Ralph's Coffee</t>
+          <t>TULLY'S COFFEE</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -27966,7 +27978,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>.17 Café</t>
+          <t>SMITH TEAMAKER</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -27989,7 +28001,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>STARBUCKS</t>
+          <t>ERIC ROSE YOKOHAMA COFFEE</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -28012,7 +28024,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>5 CROSSTIES COFFEE</t>
+          <t>Ralph's Coffee</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -28022,7 +28034,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>エキュートエディション横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
@@ -28035,7 +28047,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>京都 茶寮翠泉</t>
+          <t>.17 Café</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -28045,7 +28057,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
@@ -28058,7 +28070,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>ラニカイジュース</t>
+          <t>STARBUCKS</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -28068,7 +28080,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
@@ -28081,7 +28093,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>AUX BACCHANALES La Sœur</t>
+          <t>5 CROSSTIES COFFEE</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -28091,7 +28103,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>エキュートエディション横浜</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -28104,7 +28116,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>果実園リーベル</t>
+          <t>京都 茶寮翠泉</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -28127,7 +28139,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>TOMCAT</t>
+          <t>ラニカイジュース</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -28150,7 +28162,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>TULLY'S COFFEE</t>
+          <t>AUX BACCHANALES La Sœur</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -28173,7 +28185,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>三本珈琲店</t>
+          <t>果実園リーベル</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -28196,7 +28208,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>BISTRO Katsuki</t>
+          <t>TOMCAT</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -28206,7 +28218,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>CIAL横浜ANNEX</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -28214,22 +28226,22 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>メガネ</t>
+          <t>ベーカリー</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>CHUO CONTACT</t>
+          <t>TULLY'S COFFEE</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
@@ -28237,22 +28249,22 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>メガネ</t>
+          <t>ベーカリー</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ジンズ</t>
+          <t>三本珈琲店</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
@@ -28260,29 +28272,25 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>メガネ</t>
+          <t>ベーカリー</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>ハートアップ（コンタクト）</t>
+          <t>BISTRO Katsuki</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>2F</t>
-        </is>
-      </c>
+          <t>CIAL横浜ANNEX</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -28292,24 +28300,20 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>ゾフ</t>
+          <t>CHUO CONTACT</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>2F</t>
-        </is>
-      </c>
+          <t>アトレ品川</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -28324,19 +28328,15 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>4F</t>
-        </is>
-      </c>
+          <t>アトレ品川</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>オグラ眼鏡店</t>
+          <t>ハートアップ（コンタクト）</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>6F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -28378,15 +28378,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -28396,20 +28400,24 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>コンタクトのアイシティ</t>
+          <t>ジンズ</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>4F</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -28419,20 +28427,24 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Stay&amp;go</t>
+          <t>オグラ眼鏡店</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>6F</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -28442,7 +28454,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>MOSCOT</t>
+          <t>ゾフ</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -28452,7 +28464,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
@@ -28465,7 +28477,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>eyecity</t>
+          <t>コンタクトのアイシティ</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -28475,7 +28487,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E334" t="inlineStr"/>
@@ -28483,22 +28495,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>リラクゼーション</t>
+          <t>メガネ</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>フットセラピー</t>
+          <t>Stay&amp;go</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
@@ -28506,22 +28518,22 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>リラクゼーション</t>
+          <t>メガネ</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>ヴェリー</t>
+          <t>MOSCOT</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
@@ -28529,29 +28541,25 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>リラクゼーション</t>
+          <t>メガネ</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>ネイルステーション</t>
+          <t>eyecity</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
+          <t>ニュウマン横浜</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -28561,24 +28569,20 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>リラクゼ</t>
+          <t>フットセラピー</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>2F</t>
-        </is>
-      </c>
+          <t>アトレ品川</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -28588,24 +28592,20 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>イレブンカット</t>
+          <t>ヴェリー</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>2F</t>
-        </is>
-      </c>
+          <t>アトレ品川</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -28615,7 +28615,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ル・タン</t>
+          <t>ネイルステーション</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -28630,7 +28630,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -28642,7 +28642,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ラフィネ/無重力マッサージ</t>
+          <t>リラクゼ</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -28669,7 +28669,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>RESET</t>
+          <t>イレブンカット</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ダッシングディバ</t>
+          <t>ル・タン</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -28711,7 +28711,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -28723,7 +28723,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ファス</t>
+          <t>ラフィネ/無重力マッサージ</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -28738,7 +28738,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>6F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -28750,7 +28750,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>アトリエJD パリ</t>
+          <t>RESET</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>8F</t>
+          <t>2F</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>エステティックサロン ソシエ/ビューティスタジオ ソシエ</t>
+          <t>ダッシングディバ</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>8F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -28804,20 +28804,24 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>NAILS INC</t>
+          <t>ファス</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>6F</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -28827,20 +28831,24 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>よこはま駅ビル眼科</t>
+          <t>アトリエJD パリ</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>8F</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -28850,20 +28858,24 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>ビューティフェイス</t>
+          <t>エステティックサロン ソシエ/ビューティスタジオ ソシエ</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>8F</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -28873,7 +28885,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>グランラフィネ</t>
+          <t>NAILS INC</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -28896,7 +28908,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>DIAMOND EYES</t>
+          <t>よこはま駅ビル眼科</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -28919,7 +28931,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>リラクゼ</t>
+          <t>ビューティフェイス</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -28942,7 +28954,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>NAIL STATION</t>
+          <t>グランラフィネ</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -28965,7 +28977,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>整体×ボディケア Refresh</t>
+          <t>DIAMOND EYES</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -28988,7 +29000,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>atelier haruka</t>
+          <t>リラクゼ</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -29011,7 +29023,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Footdesign</t>
+          <t>NAIL STATION</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -29021,7 +29033,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
@@ -29034,7 +29046,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>整体×ボディケア Refresh</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -29044,7 +29056,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
@@ -29057,7 +29069,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>ジェクサー・フィットネススタジオ マシンピラティス</t>
+          <t>atelier haruka</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -29067,7 +29079,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
@@ -29080,7 +29092,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>横浜MKアイクリニック</t>
+          <t>Footdesign</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -29098,22 +29110,22 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>レストラン</t>
+          <t>リラクゼーション</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Antenna America</t>
+          <t>Violet</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
@@ -29121,22 +29133,22 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>レストラン</t>
+          <t>リラクゼーション</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>よいのいき</t>
+          <t>ジェクサー・フィットネススタジオ マシンピラティス</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E361" t="inlineStr"/>
@@ -29144,22 +29156,22 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>レストラン</t>
+          <t>リラクゼーション</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>custom salad Veggie</t>
+          <t>横浜MKアイクリニック</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>品川</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>アトレ品川</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
@@ -29172,7 +29184,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>T.N.MEAT WORKS PREMIUM BEEF&amp;WINE</t>
+          <t>Antenna America</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -29195,7 +29207,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Guzman y Gomez</t>
+          <t>よいのいき</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -29218,7 +29230,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>CHICKEN NAN-BAR by TSUKADA NOJO</t>
+          <t>custom salad Veggie</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -29241,7 +29253,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>モスバーガー</t>
+          <t>T.N.MEAT WORKS PREMIUM BEEF&amp;WINE</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -29264,7 +29276,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>サラベス</t>
+          <t>Guzman y Gomez</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -29287,7 +29299,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>モンドバー</t>
+          <t>CHICKEN NAN-BAR by TSUKADA NOJO</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -29310,7 +29322,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ざ ぜん</t>
+          <t>モスバーガー</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -29333,7 +29345,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>つばめKITCHEN</t>
+          <t>サラベス</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -29356,7 +29368,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Asian Kitchen サナギ</t>
+          <t>モンドバー</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -29379,7 +29391,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>エーダブリュ ゴーゴー</t>
+          <t>ざ ぜん</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -29402,7 +29414,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ベルジアン・ブラッスリー・コート ルーヴェン</t>
+          <t>つばめKITCHEN</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -29425,7 +29437,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>IVO HOME'SPASTA Trattoria</t>
+          <t>Asian Kitchen サナギ</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -29448,7 +29460,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>エル カリエンテ</t>
+          <t>エーダブリュ ゴーゴー</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -29471,7 +29483,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>グランド・セントラル・オイスター・バー＆レストラン</t>
+          <t>ベルジアン・ブラッスリー・コート ルーヴェン</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -29494,7 +29506,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>海鮮寿し トリトン</t>
+          <t>IVO HOME'SPASTA Trattoria</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -29517,7 +29529,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>シターラダイナー</t>
+          <t>エル カリエンテ</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -29527,7 +29539,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -29540,7 +29552,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ぬる燗佐藤 御殿山茶寮</t>
+          <t>グランド・セントラル・オイスター・バー＆レストラン</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -29550,7 +29562,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -29563,7 +29575,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>築地 竹若</t>
+          <t>海鮮寿し トリトン</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -29573,7 +29585,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>エキュート品川</t>
+          <t>アトレ品川</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
@@ -29586,7 +29598,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ミスターチキン鶏飯店</t>
+          <t>シターラダイナー</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -29609,7 +29621,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>TOKYO豚骨BASE MADE by 一風堂</t>
+          <t>ぬる燗佐藤 御殿山茶寮</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -29632,7 +29644,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>手延べうどん 水山</t>
+          <t>築地 竹若</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -29655,7 +29667,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>スパイスファクトリー</t>
+          <t>ミスターチキン鶏飯店</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -29678,7 +29690,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>吉利庵</t>
+          <t>TOKYO豚骨BASE MADE by 一風堂</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -29701,7 +29713,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>品川 ひおき</t>
+          <t>手延べうどん 水山</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -29724,7 +29736,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>立喰い寿司 魚がし日本一</t>
+          <t>スパイスファクトリー</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -29747,7 +29759,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>関谷スパゲティ EXPRESS</t>
+          <t>吉利庵</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -29770,24 +29782,20 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>たんめん専門店 百菜</t>
+          <t>品川 ひおき</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -29797,24 +29805,20 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>らぁめん大山</t>
+          <t>立喰い寿司 魚がし日本一</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -29824,24 +29828,20 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>焼きあご塩らー麺たかはし</t>
+          <t>関谷スパゲティ EXPRESS</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>品川</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>B1F</t>
-        </is>
-      </c>
+          <t>エキュート品川</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -29851,7 +29851,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>なんつッ亭</t>
+          <t>たんめん専門店 百菜</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -29878,7 +29878,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>大阪焼肉・ホルモン ふたご</t>
+          <t>らぁめん大山</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -29893,7 +29893,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -29905,7 +29905,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>ふたば製麺</t>
+          <t>焼きあご塩らー麺たかはし</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -29920,7 +29920,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>舎鈴</t>
+          <t>なんつッ亭</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -29947,7 +29947,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>北側改札内3F</t>
+          <t>B1F</t>
         </is>
       </c>
     </row>
@@ -29959,7 +29959,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>スープ ストック トーキョー</t>
+          <t>大阪焼肉・ホルモン ふたご</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -29986,7 +29986,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>プラチナ ビア マルシェ</t>
+          <t>ふたば製麺</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -30001,7 +30001,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -30013,7 +30013,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>白金魚プラチナフィッシュクラフト ビア バル</t>
+          <t>舎鈴</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -30028,7 +30028,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>北側改札内3F</t>
         </is>
       </c>
     </row>
@@ -30040,7 +30040,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>プロント</t>
+          <t>スープ ストック トーキョー</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -30055,7 +30055,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>1F</t>
         </is>
       </c>
     </row>
@@ -30067,7 +30067,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>どうとんぼり神座</t>
+          <t>プラチナ ビア マルシェ</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -30094,7 +30094,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>そばじ</t>
+          <t>白金魚プラチナフィッシュクラフト ビア バル</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -30121,7 +30121,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>コレもう食べた？</t>
+          <t>プロント</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -30148,7 +30148,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>こめらく 海鮮ごはんと和のスープ。</t>
+          <t>どうとんぼり神座</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -30175,7 +30175,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>WithGreen</t>
+          <t>そばじ</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -30202,7 +30202,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>フタバフルーツパーラー</t>
+          <t>コレもう食べた？</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -30217,7 +30217,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>4F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -30229,7 +30229,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>イー・エー・グラン</t>
+          <t>こめらく 海鮮ごはんと和のスープ。</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>4F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -30256,7 +30256,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>トラットリア ターヴォラ</t>
+          <t>WithGreen</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -30271,7 +30271,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>4F</t>
+          <t>3F</t>
         </is>
       </c>
     </row>
@@ -30283,7 +30283,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>カフェ ノリータ</t>
+          <t>フタバフルーツパーラー</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>コーヒー＆ワインスタンド トロッコ</t>
+          <t>イー・エー・グラン</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -30337,7 +30337,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>肉食べ放題BBQビアガーデン</t>
+          <t>トラットリア ターヴォラ</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -30352,7 +30352,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>6F</t>
+          <t>4F</t>
         </is>
       </c>
     </row>
@@ -30364,7 +30364,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>かっぱ寿司</t>
+          <t>カフェ ノリータ</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -30379,7 +30379,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>7F</t>
+          <t>4F</t>
         </is>
       </c>
     </row>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>ラパウザ</t>
+          <t>コーヒー＆ワインスタンド トロッコ</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -30406,7 +30406,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>7F</t>
+          <t>4F</t>
         </is>
       </c>
     </row>
@@ -30418,7 +30418,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>とんかつ和幸</t>
+          <t>肉食べ放題BBQビアガーデン</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -30433,7 +30433,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>7F</t>
+          <t>6F</t>
         </is>
       </c>
     </row>
@@ -30445,7 +30445,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>卵と私</t>
+          <t>かっぱ寿司</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -30472,7 +30472,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>牛たん とろろ 麦めし ねぎし</t>
+          <t>ラパウザ</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>しゃぶ葉</t>
+          <t>とんかつ和幸</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -30526,7 +30526,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>星のうどん庵</t>
+          <t>卵と私</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -30553,7 +30553,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>こてがえし</t>
+          <t>牛たん とろろ 麦めし ねぎし</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>8F</t>
+          <t>7F</t>
         </is>
       </c>
     </row>
@@ -30580,7 +30580,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>ジョナサン</t>
+          <t>しゃぶ葉</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -30595,7 +30595,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>8F</t>
+          <t>7F</t>
         </is>
       </c>
     </row>
@@ -30607,20 +30607,24 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>The French Toast Factory</t>
+          <t>星のうどん庵</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>7F</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -30630,20 +30634,24 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>オッティモシーフードガーデン</t>
+          <t>こてがえし</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>8F</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -30653,20 +30661,24 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>マンゴツリーカフェ</t>
+          <t>ジョナサン</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>横浜</t>
+          <t>川崎</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>ルミネ横浜</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr"/>
+          <t>アトレ川崎</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>8F</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -30676,7 +30688,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>マルモキッチン</t>
+          <t>The French Toast Factory</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -30699,7 +30711,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>ソバキチ</t>
+          <t>オッティモシーフードガーデン</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -30722,7 +30734,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>洋食と喫茶 咖喱屋ボングー</t>
+          <t>マンゴツリーカフェ</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -30745,7 +30757,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>韓美膳</t>
+          <t>マルモキッチン</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -30768,7 +30780,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>神戸元町ドリア</t>
+          <t>ソバキチ</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -30791,7 +30803,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>cafe locally</t>
+          <t>洋食と喫茶 咖喱屋ボングー</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -30814,7 +30826,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>韓美膳</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -30837,7 +30849,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>ご馳走汁と炊き込みご飯 七五三</t>
+          <t>神戸元町ドリア</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -30860,7 +30872,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>ラ・メゾン アンソレイユターブル</t>
+          <t>cafe locally</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -30883,7 +30895,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>やさい家めい</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -30906,7 +30918,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>土古里</t>
+          <t>ご馳走汁と炊き込みご飯 七五三</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -30929,7 +30941,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>京都 石塀小路豆ちゃ</t>
+          <t>ラ・メゾン アンソレイユターブル</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -30952,7 +30964,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>黒ぶたや</t>
+          <t>やさい家めい</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -30975,7 +30987,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>ブリル飯店</t>
+          <t>土古里</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -30998,7 +31010,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>牛たん炭焼 利久</t>
+          <t>京都 石塀小路豆ちゃ</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -31021,7 +31033,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>つばめグリル</t>
+          <t>黒ぶたや</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -31044,7 +31056,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>the Rooftop club</t>
+          <t>ブリル飯店</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -31067,7 +31079,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>THE ALLEY</t>
+          <t>牛たん炭焼 利久</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -31077,7 +31089,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -31090,7 +31102,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>THE CITY BAKERY</t>
+          <t>つばめグリル</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -31100,7 +31112,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -31113,7 +31125,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>HARBS</t>
+          <t>the Rooftop club</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -31123,7 +31135,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>ニュウマン横浜</t>
+          <t>ルミネ横浜</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -31136,7 +31148,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2416 MARKET</t>
+          <t>THE ALLEY</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -31159,7 +31171,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2416 MARKET PASTA&amp;</t>
+          <t>THE CITY BAKERY</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -31182,7 +31194,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>800°DEGREES CRAFT BREW STAND</t>
+          <t>HARBS</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -31205,7 +31217,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>800°DEGREES ARTISAN PIZZERIA</t>
+          <t>2416 MARKET</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -31228,7 +31240,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>CRISP SALAD WORKS</t>
+          <t>2416 MARKET PASTA&amp;</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -31251,7 +31263,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SALON BUTCHER &amp; WINE</t>
+          <t>800°DEGREES CRAFT BREW STAND</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -31274,7 +31286,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>THE CITY BAKERY BRASSERIE RUBIN</t>
+          <t>800°DEGREES ARTISAN PIZZERIA</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -31297,7 +31309,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>しらす食堂 じゃこ屋 七代目 山利</t>
+          <t>CRISP SALAD WORKS</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -31320,7 +31332,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>SUSHI TOKYO TEN</t>
+          <t>SALON BUTCHER &amp; WINE</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -31343,7 +31355,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Nood e</t>
+          <t>THE CITY BAKERY BRASSERIE RUBIN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -31366,7 +31378,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>PARIYA DELICATESSEN</t>
+          <t>しらす食堂 じゃこ屋 七代目 山利</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -31389,7 +31401,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>MS.CASABLANCA</t>
+          <t>SUSHI TOKYO TEN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -31412,7 +31424,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>横浜DRAセブン</t>
+          <t>Nood e</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -31435,7 +31447,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>COMEDOR DE MARGARITA</t>
+          <t>PARIYA DELICATESSEN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -31458,7 +31470,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>蕎麦 蘇枋</t>
+          <t>MS.CASABLANCA</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -31481,7 +31493,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>BETELNUT</t>
+          <t>横浜DRAセブン</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -31504,7 +31516,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>うなぎと和食 八十八</t>
+          <t>COMEDOR DE MARGARITA</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -31527,7 +31539,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>横浜焼肉 kintan</t>
+          <t>蕎麦 蘇枋</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -31550,7 +31562,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>貝出汁粥 鬼貝</t>
+          <t>BETELNUT</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -31560,7 +31572,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>エキュートエディション横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
@@ -31573,7 +31585,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>大衆酒場2.0 とぽす</t>
+          <t>うなぎと和食 八十八</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -31583,7 +31595,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>エキュートエディション横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E462" t="inlineStr"/>
@@ -31596,7 +31608,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>チョイット・コンセプト</t>
+          <t>横浜焼肉 kintan</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -31606,7 +31618,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>エキュートエディション横浜</t>
+          <t>ニュウマン横浜</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -31619,7 +31631,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>横浜すし好</t>
+          <t>貝出汁粥 鬼貝</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -31642,7 +31654,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>COFFEE AND BEER &amp;9（アンド・ナイン）</t>
+          <t>大衆酒場2.0 とぽす</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -31665,7 +31677,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>元祖油堂</t>
+          <t>チョイット・コンセプト</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -31675,7 +31687,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>エキュートエディション横浜</t>
         </is>
       </c>
       <c r="E466" t="inlineStr"/>
@@ -31688,7 +31700,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>AMARA INDIAN CURRY ＆ NAN</t>
+          <t>横浜すし好</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -31698,7 +31710,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>エキュートエディション横浜</t>
         </is>
       </c>
       <c r="E467" t="inlineStr"/>
@@ -31711,7 +31723,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>揚げたて天ぷら はま天</t>
+          <t>COFFEE AND BEER &amp;9（アンド・ナイン）</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -31721,7 +31733,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>CIAL横浜</t>
+          <t>エキュートエディション横浜</t>
         </is>
       </c>
       <c r="E468" t="inlineStr"/>
@@ -31734,7 +31746,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>CRAFT BEER TAP⑨</t>
+          <t>元祖油堂</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -31757,7 +31769,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>#海南鶏飯食堂</t>
+          <t>AMARA INDIAN CURRY ＆ NAN</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -31780,7 +31792,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>右衛門</t>
+          <t>揚げたて天ぷら はま天</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -31803,7 +31815,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>ごっつええ本舗</t>
+          <t>CRAFT BEER TAP⑨</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -31826,7 +31838,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>立ち寿司 おや潮</t>
+          <t>#海南鶏飯食堂</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -31849,7 +31861,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>極味薬膳スープ 菜菜麻辣湯</t>
+          <t>右衛門</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -31872,7 +31884,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Bar＆Tapas Celona</t>
+          <t>ごっつええ本舗</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -31895,7 +31907,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>CYCLO Banh mi</t>
+          <t>立ち寿司 おや潮</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -31918,7 +31930,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>つけめんTETSU</t>
+          <t>極味薬膳スープ 菜菜麻辣湯</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -31941,7 +31953,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>鉄板韓国 SHIK-TTANG</t>
+          <t>Bar＆Tapas Celona</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -31964,7 +31976,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>ハマチカ酒場</t>
+          <t>CYCLO Banh mi</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -31987,7 +31999,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>磯丸水産食堂</t>
+          <t>つけめんTETSU</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -32010,7 +32022,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>ちゃんぷら～</t>
+          <t>鉄板韓国 SHIK-TTANG</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -32033,7 +32045,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>串カツ田中</t>
+          <t>ハマチカ酒場</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -32056,7 +32068,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>新潟・佐渡の旬と地酒 いかの墨</t>
+          <t>磯丸水産食堂</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -32066,7 +32078,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>CIAL横浜ANNEX</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E483" t="inlineStr"/>
@@ -32079,7 +32091,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>シュマッツ・ビア・ダイニング</t>
+          <t>ちゃんぷら～</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -32089,7 +32101,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>CIAL横浜ANNEX</t>
+          <t>CIAL横浜</t>
         </is>
       </c>
       <c r="E484" t="inlineStr"/>
@@ -32097,83 +32109,71 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>レストラン</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>TAKUJI STATION</t>
+          <t>串カツ田中</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr">
-        <is>
-          <t>2F</t>
-        </is>
-      </c>
+          <t>CIAL横浜</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>レストラン</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>めばえ教室</t>
+          <t>新潟・佐渡の旬と地酒 いかの墨</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>7F</t>
-        </is>
-      </c>
+          <t>CIAL横浜ANNEX</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>子供服</t>
+          <t>レストラン</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>ミキハウスキッズパル</t>
+          <t>シュマッツ・ビア・ダイニング</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>川崎</t>
+          <t>横浜</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>アトレ川崎</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>7F</t>
-        </is>
-      </c>
+          <t>CIAL横浜ANNEX</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
